--- a/Kaspi_Financial_Analysis.xlsx
+++ b/Kaspi_Financial_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consulting\Kaspi Bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9E1EAF-5427-4650-9878-B53F36B80E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168F65F1-69A1-4173-9EEE-4AE00880C2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{74D3D57B-FAE8-45A6-AD25-DA4D42E998AB}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="143">
   <si>
     <t>.</t>
   </si>
@@ -164,9 +164,6 @@
     <t>2026E Fintech Revenue</t>
   </si>
   <si>
-    <t>Total 2026E KZ Revenue</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -198,18 +195,284 @@
   </si>
   <si>
     <t>Bull Case</t>
+  </si>
+  <si>
+    <t>Blended revenue / GMV (incl. 1P)</t>
+  </si>
+  <si>
+    <t>Revenue reconciliation inputs</t>
+  </si>
+  <si>
+    <t>Revenue by geography: Kazakhstan and other</t>
+  </si>
+  <si>
+    <t>Revenue by geography: Türkiye</t>
+  </si>
+  <si>
+    <t>Rewards (contra-revenue)</t>
+  </si>
+  <si>
+    <t>Revenue Reconciliation (KZT million)</t>
+  </si>
+  <si>
+    <t>Payments segment revenue</t>
+  </si>
+  <si>
+    <t>Marketplace segment revenue</t>
+  </si>
+  <si>
+    <t>Fintech segment revenue</t>
+  </si>
+  <si>
+    <t>Sum of segment revenues (pre-eliminations)</t>
+  </si>
+  <si>
+    <t>Less: intersegment eliminations</t>
+  </si>
+  <si>
+    <t>Less: rewards</t>
+  </si>
+  <si>
+    <t>Consolidated revenue (reconstructed)</t>
+  </si>
+  <si>
+    <t>Consolidated revenue (reported)</t>
+  </si>
+  <si>
+    <t>Check (must be 0)</t>
+  </si>
+  <si>
+    <t>Eliminations + rewards, % of segment sum</t>
+  </si>
+  <si>
+    <t>Total 2026E KZ segment revenue (pre-eliminations)</t>
+  </si>
+  <si>
+    <t>2025 KZ baseline (segment basis)</t>
+  </si>
+  <si>
+    <t>Segment detail inputs</t>
+  </si>
+  <si>
+    <t>Payments fee revenue</t>
+  </si>
+  <si>
+    <t>Payments interest revenue</t>
+  </si>
+  <si>
+    <t>Marketplace fee revenue (group)</t>
+  </si>
+  <si>
+    <t>…of which Türkiye</t>
+  </si>
+  <si>
+    <t>Marketplace 3P GMV (KZ)</t>
+  </si>
+  <si>
+    <t>Marketplace 1P GMV (KZ)</t>
+  </si>
+  <si>
+    <t>Marketplace retail revenue (group)</t>
+  </si>
+  <si>
+    <t>Marketplace interest revenue (group)</t>
+  </si>
+  <si>
+    <t>Marketplace other gains (group)</t>
+  </si>
+  <si>
+    <t>Fintech interest revenue</t>
+  </si>
+  <si>
+    <t>Fintech fee revenue</t>
+  </si>
+  <si>
+    <t>Fintech other gains/(losses)</t>
+  </si>
+  <si>
+    <t>Average Net Loan Portfolio</t>
+  </si>
+  <si>
+    <t>Fintech Yield (20-F KPI, reference only)</t>
+  </si>
+  <si>
+    <t>Cost of Risk (for later)</t>
+  </si>
+  <si>
+    <t>2,1%</t>
+  </si>
+  <si>
+    <t>2,2%</t>
+  </si>
+  <si>
+    <t>Corrected Unit Economics</t>
+  </si>
+  <si>
+    <t>Payments fee take rate (fee rev / TPV)</t>
+  </si>
+  <si>
+    <t>KZ Marketplace fee revenue</t>
+  </si>
+  <si>
+    <t>Marketplace take rate (KZ fee / 3P GMV)</t>
+  </si>
+  <si>
+    <t>KZ other marketplace revenue (1P retail + interest + gains)</t>
+  </si>
+  <si>
+    <t>Blended revenue / total GMV</t>
+  </si>
+  <si>
+    <t>Fintech revenue excl. other gains</t>
+  </si>
+  <si>
+    <t>Fintech yield on Avg Net Loan Portfolio (model basis)</t>
+  </si>
+  <si>
+    <t>TFV-to-portfolio conversion</t>
+  </si>
+  <si>
+    <t>Fee share of Fintech revenue</t>
+  </si>
+  <si>
+    <t>Check: row 68 − row 23 (must be 0)</t>
+  </si>
+  <si>
+    <t>Fee (take rate effect)</t>
+  </si>
+  <si>
+    <t>1P retail</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>Other gains</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TPV growth</t>
+  </si>
+  <si>
+    <t>Payments fee take rate</t>
+  </si>
+  <si>
+    <t>Payments interest revenue growth</t>
+  </si>
+  <si>
+    <t>3P GMV growth</t>
+  </si>
+  <si>
+    <t>Marketplace take rate</t>
+  </si>
+  <si>
+    <t>Other marketplace revenue growth</t>
+  </si>
+  <si>
+    <t>TFV growth</t>
+  </si>
+  <si>
+    <t>Fintech yield (model basis)</t>
+  </si>
+  <si>
+    <t>Bear (C)</t>
+  </si>
+  <si>
+    <t>Base (D)</t>
+  </si>
+  <si>
+    <t>Bull (E)</t>
+  </si>
+  <si>
+    <t>2025 replay (F)</t>
+  </si>
+  <si>
+    <t>Cost of Risk (CoR)</t>
+  </si>
+  <si>
+    <t>Bear</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Bull</t>
+  </si>
+  <si>
+    <t>Anchor</t>
+  </si>
+  <si>
+    <t>Marketplace Revenue (KZ)</t>
+  </si>
+  <si>
+    <t>Fintech Revenue (Gross)</t>
+  </si>
+  <si>
+    <t>Fintech Cost of Risk (Losses)</t>
+  </si>
+  <si>
+    <t>Fintech Net Revenue (Post-Risk)</t>
+  </si>
+  <si>
+    <t>Total Ecosystem Revenue (Gross)</t>
+  </si>
+  <si>
+    <t>Total Ecosystem Revenue (Net of Risk)</t>
+  </si>
+  <si>
+    <t>YoY vs 2025 Gross (Check)</t>
+  </si>
+  <si>
+    <t>Cost Layer &amp; Net Income</t>
+  </si>
+  <si>
+    <t>Payments Net Margin (%)</t>
+  </si>
+  <si>
+    <t>Marketplace Net Margin (%)</t>
+  </si>
+  <si>
+    <t>Fintech Cost of Funds (% of Portfolio)</t>
+  </si>
+  <si>
+    <t>Fintech OPEX &amp; Tax (% of Gross Rev)</t>
+  </si>
+  <si>
+    <t>Payments Net Income</t>
+  </si>
+  <si>
+    <t>Marketplace Net Income (KZ)</t>
+  </si>
+  <si>
+    <t>Fintech Interest Expense</t>
+  </si>
+  <si>
+    <t>Fintech OPEX &amp; Tax</t>
+  </si>
+  <si>
+    <t>Fintech Net Income</t>
+  </si>
+  <si>
+    <t>Consolidated Net Income (KZ)</t>
+  </si>
+  <si>
+    <t>Net Income Margin (Ecosystem)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -247,6 +510,12 @@
       <sz val="14"/>
       <color theme="0"/>
       <name val="Inter Tight Medium"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Inter Tight"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -304,7 +573,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -354,13 +623,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -370,6 +633,66 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1007,7 +1330,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total 2026E KZ Revenue</c:v>
+                  <c:v>Total 2026E KZ segment revenue (pre-eliminations)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1653,10 +1976,10 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.41699999999999998</c:v>
+                  <c:v>0.41736528081208268</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.26400000000000001</c:v>
+                  <c:v>0.26388716568209086</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3995,13 +4318,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A88866-A1AE-4376-A066-EACDBAE1C6EE}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.640625" customWidth="1"/>
-    <col min="2" max="2" width="26.5" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
     <col min="3" max="3" width="9.0703125" customWidth="1"/>
     <col min="4" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.5">
@@ -4179,7 +4503,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B17" t="s">
         <v>23</v>
       </c>
@@ -4190,11 +4514,11 @@
         <v>0</v>
       </c>
       <c r="E17" s="18">
-        <f>302921+638164+54269</f>
-        <v>995354</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.5">
+        <f>E22</f>
+        <v>1031592</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B18" t="s">
         <v>24</v>
       </c>
@@ -4206,6 +4530,278 @@
       </c>
       <c r="E18" s="18">
         <v>1179141</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="22">
+        <v>2586381</v>
+      </c>
+      <c r="E21" s="22">
+        <v>3070369</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="28">
+        <v>0</v>
+      </c>
+      <c r="E22" s="22">
+        <v>1031592</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="22">
+        <v>54225</v>
+      </c>
+      <c r="E23" s="22">
+        <v>55887</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B25" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="42">
+        <v>458953</v>
+      </c>
+      <c r="E26" s="42">
+        <v>510763</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="42">
+        <v>128144</v>
+      </c>
+      <c r="E27" s="42">
+        <v>147963</v>
+      </c>
+      <c r="F27" s="40">
+        <f>E26+E27-E4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="42">
+        <v>562283</v>
+      </c>
+      <c r="E28" s="42">
+        <v>974269</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="43">
+        <v>0</v>
+      </c>
+      <c r="E29" s="42">
+        <v>302921</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="42">
+        <v>5797000</v>
+      </c>
+      <c r="E30" s="42">
+        <v>6423000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="42">
+        <v>178000</v>
+      </c>
+      <c r="E31" s="42">
+        <v>234000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="42">
+        <v>163134</v>
+      </c>
+      <c r="E32" s="42">
+        <v>850127</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="43">
+        <v>0</v>
+      </c>
+      <c r="E33" s="42">
+        <v>638164</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="42">
+        <v>6304</v>
+      </c>
+      <c r="E34" s="42">
+        <v>69886</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="43">
+        <v>0</v>
+      </c>
+      <c r="E35" s="42">
+        <v>54269</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="42">
+        <v>1222</v>
+      </c>
+      <c r="E36" s="42">
+        <v>37190</v>
+      </c>
+      <c r="F36" s="16">
+        <f>E28+E32+E34+E36-E5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="43">
+        <v>0</v>
+      </c>
+      <c r="E37" s="42">
+        <v>36238</v>
+      </c>
+      <c r="F37" s="16">
+        <f>D28+D32+D34+D36-D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="42">
+        <v>955528</v>
+      </c>
+      <c r="E38" s="42">
+        <v>1383465</v>
+      </c>
+      <c r="F38" s="40">
+        <f>E29+E33+E35+E37-E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="42">
+        <v>316292</v>
+      </c>
+      <c r="E39" s="42">
+        <v>178409</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="42">
+        <v>10007</v>
+      </c>
+      <c r="E40" s="42">
+        <v>-18940</v>
+      </c>
+      <c r="F40" s="16">
+        <f>E38+E39+E40-E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="42">
+        <v>4895000</v>
+      </c>
+      <c r="E41" s="42">
+        <v>6415000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="39">
+        <v>0.24</v>
+      </c>
+      <c r="E42" s="39">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -4216,15 +4812,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B0785C-78F9-4626-9FC5-2C19389EC9FB}">
-  <dimension ref="B2:K40"/>
+  <dimension ref="B2:K118"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.640625" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.0703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.2109375" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.2109375" customWidth="1"/>
     <col min="10" max="10" width="14.640625" customWidth="1"/>
     <col min="11" max="11" width="17.0703125" customWidth="1"/>
@@ -4364,11 +4960,11 @@
       </c>
       <c r="D18" s="16">
         <f>Raw_Data!E5 - Raw_Data!E17</f>
-        <v>936118</v>
+        <v>899880</v>
       </c>
       <c r="E18" s="5">
         <f>(D18/C18)-1</f>
-        <v>0.27720436650599023</v>
+        <v>0.22776259545421684</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5">
@@ -4377,7 +4973,7 @@
       </c>
       <c r="D19" s="5">
         <f>Raw_Data!E17 / (Raw_Data!E5 - Raw_Data!D5)</f>
-        <v>0.83047969636112262</v>
+        <v>0.86071509325181117</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
@@ -4401,7 +4997,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B23" s="12" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C23" s="5">
         <f>Raw_Data!D5 / Raw_Data!D10</f>
@@ -4409,7 +5005,7 @@
       </c>
       <c r="D23" s="5">
         <f>(Raw_Data!E5 - Raw_Data!E17) / Raw_Data!E10</f>
-        <v>0.14062160132191678</v>
+        <v>0.13517800811176206</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.5">
@@ -4461,7 +5057,7 @@
       </c>
       <c r="D27" s="18">
         <f>D18 / Raw_Data!E14</f>
-        <v>106377.04545454544</v>
+        <v>102259.0909090909</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.5">
@@ -4481,23 +5077,23 @@
       <c r="B30" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="E30" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="28" t="s">
-        <v>55</v>
-      </c>
       <c r="I30" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J30" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.5">
@@ -4514,7 +5110,7 @@
         <v>0.2</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J31">
         <v>732943</v>
@@ -4537,7 +5133,7 @@
         <v>1.52E-2</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J32">
         <v>936118</v>
@@ -4574,13 +5170,13 @@
         <v>0.155</v>
       </c>
       <c r="I34" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K34" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="J34" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="K34" s="27" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.5">
@@ -4600,10 +5196,12 @@
         <v>2024</v>
       </c>
       <c r="J35" s="18">
+        <f>Raw_Data!D3</f>
         <v>2532156</v>
       </c>
-      <c r="K35" s="26">
-        <v>0.41699999999999998</v>
+      <c r="K35" s="24">
+        <f>C15</f>
+        <v>0.41736528081208268</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.5">
@@ -4623,14 +5221,16 @@
         <v>2025</v>
       </c>
       <c r="J36" s="18">
+        <f>Raw_Data!E3</f>
         <v>4046074</v>
       </c>
-      <c r="K36" s="26">
-        <v>0.26400000000000001</v>
+      <c r="K36" s="24">
+        <f>D15</f>
+        <v>0.26388716568209086</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C37" s="21">
@@ -4680,21 +5280,966 @@
         <v>1869912.9600000002</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B40" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="23">
+    <row r="40" spans="2:11" ht="42" x14ac:dyDescent="0.5">
+      <c r="B40" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="36">
         <f>SUM(C37:C39)</f>
         <v>3286656.1300000004</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="36">
         <f>SUM(D37:D39)</f>
         <v>3576801.6849999996</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="36">
         <f>SUM(E37:E39)</f>
         <v>3894032.8200000003</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="34">
+        <v>2024</v>
+      </c>
+      <c r="D42" s="34">
+        <v>2025</v>
+      </c>
+      <c r="E42" s="30"/>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B43" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="32">
+        <f>Raw_Data!D4</f>
+        <v>587097</v>
+      </c>
+      <c r="D43" s="32">
+        <f>Raw_Data!E4</f>
+        <v>658726</v>
+      </c>
+      <c r="E43" s="30"/>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B44" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="32">
+        <f>Raw_Data!D5</f>
+        <v>732943</v>
+      </c>
+      <c r="D44" s="32">
+        <f>Raw_Data!E5</f>
+        <v>1931472</v>
+      </c>
+      <c r="E44" s="30"/>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B45" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="32">
+        <f>Raw_Data!D6</f>
+        <v>1281827</v>
+      </c>
+      <c r="D45" s="32">
+        <f>Raw_Data!E6</f>
+        <v>1542934</v>
+      </c>
+      <c r="E45" s="30"/>
+    </row>
+    <row r="46" spans="2:11" ht="42" x14ac:dyDescent="0.5">
+      <c r="B46" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="32">
+        <f>SUM(C43:C45)</f>
+        <v>2601867</v>
+      </c>
+      <c r="D46" s="32">
+        <f>SUM(D43:D45)</f>
+        <v>4133132</v>
+      </c>
+      <c r="E46" s="30"/>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B47" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="51">
+        <f>-(C46-(Raw_Data!D21+Raw_Data!D22))</f>
+        <v>-15486</v>
+      </c>
+      <c r="D47" s="51">
+        <f>-(D46-(Raw_Data!E21+Raw_Data!E22))</f>
+        <v>-31171</v>
+      </c>
+      <c r="E47" s="30"/>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B48" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="51">
+        <f>-Raw_Data!D23</f>
+        <v>-54225</v>
+      </c>
+      <c r="D48" s="51">
+        <f>-Raw_Data!E23</f>
+        <v>-55887</v>
+      </c>
+      <c r="E48" s="30"/>
+    </row>
+    <row r="49" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B49" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="32">
+        <f>C46+C47+C48</f>
+        <v>2532156</v>
+      </c>
+      <c r="D49" s="32">
+        <f>D46+D47+D48</f>
+        <v>4046074</v>
+      </c>
+      <c r="E49" s="30"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B50" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="32">
+        <f>Raw_Data!D3</f>
+        <v>2532156</v>
+      </c>
+      <c r="D50" s="32">
+        <f>Raw_Data!E3</f>
+        <v>4046074</v>
+      </c>
+      <c r="E50" s="30"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B51" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="32">
+        <f>C49-C50</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="32">
+        <f>D49-D50</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="30"/>
+    </row>
+    <row r="52" spans="2:5" ht="42" x14ac:dyDescent="0.5">
+      <c r="B52" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="33">
+        <f>-(C47+C48)/C46</f>
+        <v>2.6792683868929502E-2</v>
+      </c>
+      <c r="D52" s="33">
+        <f>-(D47+D48)/D46</f>
+        <v>2.1063445348466974E-2</v>
+      </c>
+      <c r="E52" s="30"/>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B58" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="16">
+        <f>Raw_Data!E4+(Raw_Data!E5-Raw_Data!E17)+Raw_Data!E6</f>
+        <v>3101540</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B62" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="17">
+        <f>Raw_Data!D26/Raw_Data!D9</f>
+        <v>1.232783582690913E-2</v>
+      </c>
+      <c r="D63" s="17">
+        <f>Raw_Data!E26/Raw_Data!E9</f>
+        <v>1.1550758723625591E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B64" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="18">
+        <f>Raw_Data!D27</f>
+        <v>128144</v>
+      </c>
+      <c r="D64" s="18">
+        <f>Raw_Data!E27</f>
+        <v>147963</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B65" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" s="18">
+        <f>Raw_Data!D28-Raw_Data!D29</f>
+        <v>562283</v>
+      </c>
+      <c r="D65" s="18">
+        <f>Raw_Data!E28-Raw_Data!E29</f>
+        <v>671348</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="42" x14ac:dyDescent="0.5">
+      <c r="B66" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C66" s="44">
+        <f>C65/Raw_Data!D30</f>
+        <v>9.6995514921511122E-2</v>
+      </c>
+      <c r="D66" s="44">
+        <f>D65/Raw_Data!E30</f>
+        <v>0.10452249727541647</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="42" x14ac:dyDescent="0.5">
+      <c r="B67" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C67" s="45">
+        <f>(Raw_Data!D32-Raw_Data!D33)+(Raw_Data!D34-Raw_Data!D35)+(Raw_Data!D36-Raw_Data!D37)</f>
+        <v>170660</v>
+      </c>
+      <c r="D67" s="45">
+        <f>(Raw_Data!E32-Raw_Data!E33)+(Raw_Data!E34-Raw_Data!E35)+(Raw_Data!E36-Raw_Data!E37)</f>
+        <v>228532</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B68" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" s="17">
+        <f>(C65+C67)/Raw_Data!D10</f>
+        <v>0.12266828451882845</v>
+      </c>
+      <c r="D68" s="17">
+        <f>(D65+D67)/Raw_Data!E10</f>
+        <v>0.13517800811176206</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B69" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" s="18">
+        <f>Raw_Data!D38+Raw_Data!D39</f>
+        <v>1271820</v>
+      </c>
+      <c r="D69" s="18">
+        <f>Raw_Data!E38+Raw_Data!E39</f>
+        <v>1561874</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" ht="42" x14ac:dyDescent="0.5">
+      <c r="B70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C70" s="44">
+        <f>C69/Raw_Data!D41</f>
+        <v>0.2598202247191011</v>
+      </c>
+      <c r="D70" s="44">
+        <f>D69/Raw_Data!E41</f>
+        <v>0.24347217459080281</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B71" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" s="46">
+        <f>Raw_Data!D11/Raw_Data!D41</f>
+        <v>2.105209397344229</v>
+      </c>
+      <c r="D71" s="46">
+        <f>Raw_Data!E11/Raw_Data!E41</f>
+        <v>1.8163678877630554</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B72" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C72" s="5">
+        <f>Raw_Data!D39/C69</f>
+        <v>0.24869242502869904</v>
+      </c>
+      <c r="D72" s="5">
+        <f>Raw_Data!E39/D69</f>
+        <v>0.11422752411526153</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B73" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="47">
+        <f>C68-C23</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="47">
+        <f>D68-D23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B75" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D75" s="48">
+        <f>(D65/Raw_Data!E10-C65/Raw_Data!D10)*10000</f>
+        <v>67.424888012304066</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B76" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" s="48">
+        <f>(Raw_Data!E32-Raw_Data!E33)/Raw_Data!E10*10000 - (Raw_Data!D32-Raw_Data!D33)/Raw_Data!D10*10000</f>
+        <v>45.378573911250783</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D77" s="48">
+        <f>((Raw_Data!E34-Raw_Data!E35)/Raw_Data!E10 - (Raw_Data!D34-Raw_Data!D35)/Raw_Data!D10)*10000</f>
+        <v>12.908888683570259</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D78" s="48">
+        <f>((Raw_Data!E36-Raw_Data!E37)/Raw_Data!E10 - (Raw_Data!D36-Raw_Data!D37)/Raw_Data!D10)*10000</f>
+        <v>-0.61511467778907036</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B79" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D79" s="48">
+        <f>SUM(D75:D78)</f>
+        <v>125.09723592933604</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="C85" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D85" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="E85" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="F85" s="49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B86" t="s">
+        <v>107</v>
+      </c>
+      <c r="C86" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="D86" s="38">
+        <v>0.15</v>
+      </c>
+      <c r="E86" s="38">
+        <v>0.2</v>
+      </c>
+      <c r="F86" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B87" t="s">
+        <v>108</v>
+      </c>
+      <c r="C87" s="50">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D87" s="50">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="E87" s="50">
+        <v>1.155E-2</v>
+      </c>
+      <c r="F87" s="50">
+        <f>D63</f>
+        <v>1.1550758723625591E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B88" t="s">
+        <v>109</v>
+      </c>
+      <c r="C88" s="38">
+        <v>-0.1</v>
+      </c>
+      <c r="D88" s="38">
+        <v>0.08</v>
+      </c>
+      <c r="E88" s="38">
+        <v>0.12</v>
+      </c>
+      <c r="F88" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B89" t="s">
+        <v>110</v>
+      </c>
+      <c r="C89" s="38">
+        <v>0.06</v>
+      </c>
+      <c r="D89" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="E89" s="38">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F89" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B90" t="s">
+        <v>111</v>
+      </c>
+      <c r="C90" s="17">
+        <v>0.1045</v>
+      </c>
+      <c r="D90" s="17">
+        <v>0.109</v>
+      </c>
+      <c r="E90" s="17">
+        <v>0.112</v>
+      </c>
+      <c r="F90" s="17">
+        <f>D66</f>
+        <v>0.10452249727541647</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B91" t="s">
+        <v>112</v>
+      </c>
+      <c r="C91" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="D91" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="E91" s="38">
+        <v>0.35</v>
+      </c>
+      <c r="F91" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B92" t="s">
+        <v>113</v>
+      </c>
+      <c r="C92" s="38">
+        <v>0.05</v>
+      </c>
+      <c r="D92" s="38">
+        <v>0.13</v>
+      </c>
+      <c r="E92" s="38">
+        <v>0.18</v>
+      </c>
+      <c r="F92" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B93" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" s="41">
+        <v>1.85</v>
+      </c>
+      <c r="D93" s="41">
+        <v>1.8</v>
+      </c>
+      <c r="E93" s="41">
+        <v>1.75</v>
+      </c>
+      <c r="F93" s="41">
+        <f>D71</f>
+        <v>1.8163678877630554</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B94" t="s">
+        <v>114</v>
+      </c>
+      <c r="C94" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="E94" s="5">
+        <v>0.245</v>
+      </c>
+      <c r="F94" s="5">
+        <f>D70</f>
+        <v>0.24347217459080281</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B95" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="D95" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E95" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="F95" s="5">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B97" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="18">
+        <f>Raw_Data!$E$9*(1+C86)*C87 + Raw_Data!$E$27*(1+C88)</f>
+        <v>668216.60000000009</v>
+      </c>
+      <c r="D97" s="18">
+        <f>Raw_Data!$E$9*(1+D86)*D87 + Raw_Data!$E$27*(1+D88)</f>
+        <v>734425.94499999995</v>
+      </c>
+      <c r="E97" s="18">
+        <f>Raw_Data!$E$9*(1+E86)*E87 + Raw_Data!$E$27*(1+E88)</f>
+        <v>778593.9</v>
+      </c>
+      <c r="F97" s="18">
+        <f>Raw_Data!$E$9*(1+F86)*F87 + Raw_Data!$E$27*(1+F88)</f>
+        <v>658726</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B98" t="s">
+        <v>124</v>
+      </c>
+      <c r="C98" s="18">
+        <f>Raw_Data!$E$30*(1+C89)*C90 + $D$67*(1+C91)</f>
+        <v>962860.90999999992</v>
+      </c>
+      <c r="D98" s="18">
+        <f>Raw_Data!$E$30*(1+D89)*D90 + $D$67*(1+D91)</f>
+        <v>1055782.7000000002</v>
+      </c>
+      <c r="E98" s="18">
+        <f>Raw_Data!$E$30*(1+E89)*E90 + $D$67*(1+E91)</f>
+        <v>1128606.8400000001</v>
+      </c>
+      <c r="F98" s="18">
+        <f>Raw_Data!$E$30*(1+F89)*F90 + $D$67*(1+F91)</f>
+        <v>899880</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B99" t="s">
+        <v>125</v>
+      </c>
+      <c r="C99" s="18">
+        <f>Raw_Data!$E$11*(1+C92)/C93*C94</f>
+        <v>1521058.3783783785</v>
+      </c>
+      <c r="D99" s="18">
+        <f>Raw_Data!$E$11*(1+D92)/D93*D94</f>
+        <v>1755567.9999999995</v>
+      </c>
+      <c r="E99" s="18">
+        <f>Raw_Data!$E$11*(1+E92)/E93*E94</f>
+        <v>1924910.4</v>
+      </c>
+      <c r="F99" s="18">
+        <f>Raw_Data!$E$11*(1+F92)/F93*F94</f>
+        <v>1561874</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B100" t="s">
+        <v>126</v>
+      </c>
+      <c r="C100" s="27">
+        <f>-(Raw_Data!$E$11*(1+C92)/C93)*C95</f>
+        <v>-330664.86486486485</v>
+      </c>
+      <c r="D100" s="27">
+        <f>-(Raw_Data!$E$11*(1+D92)/D93)*D95</f>
+        <v>-182871.66666666663</v>
+      </c>
+      <c r="E100" s="27">
+        <f>-(Raw_Data!$E$11*(1+E92)/E93)*E95</f>
+        <v>-157135.54285714286</v>
+      </c>
+      <c r="F100" s="27">
+        <f>-(Raw_Data!$E$11*(1+F92)/F93)*F95</f>
+        <v>-141130</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B101" t="s">
+        <v>127</v>
+      </c>
+      <c r="C101" s="18">
+        <f>C99+C100</f>
+        <v>1190393.5135135136</v>
+      </c>
+      <c r="D101" s="18">
+        <f>D99+D100</f>
+        <v>1572696.333333333</v>
+      </c>
+      <c r="E101" s="18">
+        <f>E99+E100</f>
+        <v>1767774.857142857</v>
+      </c>
+      <c r="F101" s="18">
+        <f>F99+F100</f>
+        <v>1420744</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B102" t="s">
+        <v>128</v>
+      </c>
+      <c r="C102" s="18">
+        <f>C97+C98+C99</f>
+        <v>3152135.8883783785</v>
+      </c>
+      <c r="D102" s="18">
+        <f>D97+D98+D99</f>
+        <v>3545776.6449999996</v>
+      </c>
+      <c r="E102" s="18">
+        <f>E97+E98+E99</f>
+        <v>3832111.14</v>
+      </c>
+      <c r="F102" s="18">
+        <f>F97+F98+F99</f>
+        <v>3120480</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B103" t="s">
+        <v>129</v>
+      </c>
+      <c r="C103" s="18">
+        <f>C97+C98+C101</f>
+        <v>2821471.0235135136</v>
+      </c>
+      <c r="D103" s="18">
+        <f>D97+D98+D101</f>
+        <v>3362904.978333333</v>
+      </c>
+      <c r="E103" s="18">
+        <f>E97+E98+E101</f>
+        <v>3674975.5971428575</v>
+      </c>
+      <c r="F103" s="18">
+        <f>F97+F98+F101</f>
+        <v>2979350</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B104" t="s">
+        <v>130</v>
+      </c>
+      <c r="C104" s="5">
+        <f>C102/$F$102-1</f>
+        <v>1.0144557368859441E-2</v>
+      </c>
+      <c r="D104" s="5">
+        <f>D102/$F$102-1</f>
+        <v>0.13629205923447651</v>
+      </c>
+      <c r="E104" s="5">
+        <f>E102/$F$102-1</f>
+        <v>0.22805181895093063</v>
+      </c>
+      <c r="F104" s="5">
+        <f>F102/$F$102-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B106" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C106" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D106" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E106" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F106" s="25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B107" t="s">
+        <v>132</v>
+      </c>
+      <c r="C107" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D107" s="5">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="E107" s="5">
+        <v>0.68</v>
+      </c>
+      <c r="F107" s="17">
+        <f>433000/$F$97</f>
+        <v>0.65732945109195628</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B108" t="s">
+        <v>133</v>
+      </c>
+      <c r="C108" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D108" s="5">
+        <v>0.311</v>
+      </c>
+      <c r="E108" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="F108" s="17">
+        <f>280000/$F$98</f>
+        <v>0.31115259812419432</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B109" t="s">
+        <v>134</v>
+      </c>
+      <c r="C109" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="D109" s="5">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="E109" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="F109" s="17">
+        <f>909000/Raw_Data!$E$41</f>
+        <v>0.14169914263445052</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B110" t="s">
+        <v>135</v>
+      </c>
+      <c r="C110" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="D110" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E110" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="F110" s="17">
+        <v>0.1004</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B112" t="s">
+        <v>136</v>
+      </c>
+      <c r="C112" s="18">
+        <f>C97*C107</f>
+        <v>400929.96</v>
+      </c>
+      <c r="D112" s="18">
+        <f t="shared" ref="D112:F112" si="0">D97*D107</f>
+        <v>482517.84586499998</v>
+      </c>
+      <c r="E112" s="18">
+        <f t="shared" si="0"/>
+        <v>529443.85200000007</v>
+      </c>
+      <c r="F112" s="18">
+        <f t="shared" si="0"/>
+        <v>433000</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B113" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" s="18">
+        <f>C98*C108</f>
+        <v>240715.22749999998</v>
+      </c>
+      <c r="D113" s="18">
+        <f t="shared" ref="D113:F113" si="1">D98*D108</f>
+        <v>328348.41970000003</v>
+      </c>
+      <c r="E113" s="18">
+        <f t="shared" si="1"/>
+        <v>395012.39400000003</v>
+      </c>
+      <c r="F113" s="18">
+        <f t="shared" si="1"/>
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B114" t="s">
+        <v>138</v>
+      </c>
+      <c r="C114" s="18">
+        <f>-(Raw_Data!$E$11*(1+C92)/C93)*C109</f>
+        <v>-1058127.5675675676</v>
+      </c>
+      <c r="D114" s="18">
+        <f>-(Raw_Data!$E$11*(1+D92)/D93)*D109</f>
+        <v>-1031396.1999999997</v>
+      </c>
+      <c r="E114" s="18">
+        <f>-(Raw_Data!$E$11*(1+E92)/E93)*E109</f>
+        <v>-942813.25714285707</v>
+      </c>
+      <c r="F114" s="18">
+        <f>-(Raw_Data!$E$11*(1+F92)/F93)*F109</f>
+        <v>-909000.00000000012</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B115" t="s">
+        <v>139</v>
+      </c>
+      <c r="C115" s="18">
+        <f>-C99*C110</f>
+        <v>-197737.5891891892</v>
+      </c>
+      <c r="D115" s="18">
+        <f t="shared" ref="D115:F115" si="2">-D99*D110</f>
+        <v>-175556.79999999996</v>
+      </c>
+      <c r="E115" s="18">
+        <f t="shared" si="2"/>
+        <v>-173241.93599999999</v>
+      </c>
+      <c r="F115" s="18">
+        <f t="shared" si="2"/>
+        <v>-156812.1496</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B116" t="s">
+        <v>140</v>
+      </c>
+      <c r="C116" s="18">
+        <f>C101+C114+C115</f>
+        <v>-65471.643243243161</v>
+      </c>
+      <c r="D116" s="18">
+        <f t="shared" ref="D116:F116" si="3">D101+D114+D115</f>
+        <v>365743.33333333337</v>
+      </c>
+      <c r="E116" s="18">
+        <f t="shared" si="3"/>
+        <v>651719.66399999999</v>
+      </c>
+      <c r="F116" s="18">
+        <f t="shared" si="3"/>
+        <v>354931.85039999988</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B117" t="s">
+        <v>141</v>
+      </c>
+      <c r="C117" s="18">
+        <f>C112+C113+C116</f>
+        <v>576173.54425675678</v>
+      </c>
+      <c r="D117" s="18">
+        <f t="shared" ref="D117:F117" si="4">D112+D113+D116</f>
+        <v>1176609.5988983335</v>
+      </c>
+      <c r="E117" s="18">
+        <f t="shared" si="4"/>
+        <v>1576175.9100000001</v>
+      </c>
+      <c r="F117" s="52">
+        <f t="shared" si="4"/>
+        <v>1067931.8503999999</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B118" t="s">
+        <v>142</v>
+      </c>
+      <c r="C118" s="17">
+        <f>C117/C102</f>
+        <v>0.18278829487683357</v>
+      </c>
+      <c r="D118" s="17">
+        <f t="shared" ref="D118:F118" si="5">D117/D102</f>
+        <v>0.33183409918318013</v>
+      </c>
+      <c r="E118" s="17">
+        <f t="shared" si="5"/>
+        <v>0.41130746275798258</v>
+      </c>
+      <c r="F118" s="17">
+        <f t="shared" si="5"/>
+        <v>0.34223319822591391</v>
       </c>
     </row>
   </sheetData>

--- a/Kaspi_Financial_Analysis.xlsx
+++ b/Kaspi_Financial_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consulting\Kaspi Bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168F65F1-69A1-4173-9EEE-4AE00880C2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707EFB8C-8E75-4159-99A0-460817265065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{74D3D57B-FAE8-45A6-AD25-DA4D42E998AB}"/>
   </bookViews>
@@ -30,10 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="143">
-  <si>
-    <t>.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="154">
   <si>
     <t>Total Revenue</t>
   </si>
@@ -119,21 +116,12 @@
     <t>Kazakhstan Standalone</t>
   </si>
   <si>
-    <t>Payments Take Rate</t>
-  </si>
-  <si>
-    <t>Marketplace Monetization</t>
-  </si>
-  <si>
     <t>GMV per Active Consumer</t>
   </si>
   <si>
     <t>YoY</t>
   </si>
   <si>
-    <t>Fintech TFV Yield</t>
-  </si>
-  <si>
     <t>Payments ARPU</t>
   </si>
   <si>
@@ -143,36 +131,12 @@
     <t>Fintech ARPU</t>
   </si>
   <si>
-    <t>Payments TPV Growth</t>
-  </si>
-  <si>
-    <t>Marketplace GMV Growth</t>
-  </si>
-  <si>
-    <t>Fintech TFV Growth</t>
-  </si>
-  <si>
-    <t>2026E Scenario Analysis (KZ)</t>
-  </si>
-  <si>
-    <t>2026E Payments Revenue</t>
-  </si>
-  <si>
-    <t>2026E Marketplace Rev (KZ)</t>
-  </si>
-  <si>
-    <t>2026E Fintech Revenue</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
     <t>2024 Marketplace</t>
   </si>
   <si>
-    <t>2025 KZ Organic</t>
-  </si>
-  <si>
     <t>Hepsiburada / Türkiye</t>
   </si>
   <si>
@@ -185,21 +149,6 @@
     <t>Net Margin (%)</t>
   </si>
   <si>
-    <t>Revenue (Billion)</t>
-  </si>
-  <si>
-    <t>Bear Case</t>
-  </si>
-  <si>
-    <t>Base Case</t>
-  </si>
-  <si>
-    <t>Bull Case</t>
-  </si>
-  <si>
-    <t>Blended revenue / GMV (incl. 1P)</t>
-  </si>
-  <si>
     <t>Revenue reconciliation inputs</t>
   </si>
   <si>
@@ -245,9 +194,6 @@
     <t>Eliminations + rewards, % of segment sum</t>
   </si>
   <si>
-    <t>Total 2026E KZ segment revenue (pre-eliminations)</t>
-  </si>
-  <si>
     <t>2025 KZ baseline (segment basis)</t>
   </si>
   <si>
@@ -299,12 +245,6 @@
     <t>Cost of Risk (for later)</t>
   </si>
   <si>
-    <t>2,1%</t>
-  </si>
-  <si>
-    <t>2,2%</t>
-  </si>
-  <si>
     <t>Corrected Unit Economics</t>
   </si>
   <si>
@@ -332,27 +272,6 @@
     <t>TFV-to-portfolio conversion</t>
   </si>
   <si>
-    <t>Fee share of Fintech revenue</t>
-  </si>
-  <si>
-    <t>Check: row 68 − row 23 (must be 0)</t>
-  </si>
-  <si>
-    <t>Fee (take rate effect)</t>
-  </si>
-  <si>
-    <t>1P retail</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>Other gains</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>TPV growth</t>
   </si>
   <si>
@@ -389,9 +308,6 @@
     <t>2025 replay (F)</t>
   </si>
   <si>
-    <t>Cost of Risk (CoR)</t>
-  </si>
-  <si>
     <t>Bear</t>
   </si>
   <si>
@@ -401,9 +317,6 @@
     <t>Bull</t>
   </si>
   <si>
-    <t>Anchor</t>
-  </si>
-  <si>
     <t>Marketplace Revenue (KZ)</t>
   </si>
   <si>
@@ -422,9 +335,6 @@
     <t>Total Ecosystem Revenue (Net of Risk)</t>
   </si>
   <si>
-    <t>YoY vs 2025 Gross (Check)</t>
-  </si>
-  <si>
     <t>Cost Layer &amp; Net Income</t>
   </si>
   <si>
@@ -434,9 +344,6 @@
     <t>Marketplace Net Margin (%)</t>
   </si>
   <si>
-    <t>Fintech Cost of Funds (% of Portfolio)</t>
-  </si>
-  <si>
     <t>Fintech OPEX &amp; Tax (% of Gross Rev)</t>
   </si>
   <si>
@@ -458,7 +365,133 @@
     <t>Consolidated Net Income (KZ)</t>
   </si>
   <si>
-    <t>Net Income Margin (Ecosystem)</t>
+    <t>Payments segment net income</t>
+  </si>
+  <si>
+    <t>Marketplace segment net income</t>
+  </si>
+  <si>
+    <t>Fintech segment net income</t>
+  </si>
+  <si>
+    <t>Hepsiburada net loss within Marketplace segment</t>
+  </si>
+  <si>
+    <t>Fintech interest expense</t>
+  </si>
+  <si>
+    <t>Fintech provision expense</t>
+  </si>
+  <si>
+    <t>Türkiye net loss (group level)</t>
+  </si>
+  <si>
+    <t>Türkiye revenue, net of rewards/eliminations</t>
+  </si>
+  <si>
+    <t>Check: KZ Net Income reconciliation</t>
+  </si>
+  <si>
+    <t>Checks</t>
+  </si>
+  <si>
+    <t>KZ net income / KZ segment revenue (pre-elim)</t>
+  </si>
+  <si>
+    <t>Group Net Income Margin (2025)</t>
+  </si>
+  <si>
+    <t>Margin ex-Türkiye (2025)</t>
+  </si>
+  <si>
+    <t>2025 ex-Türkiye</t>
+  </si>
+  <si>
+    <t>2025 Group</t>
+  </si>
+  <si>
+    <t>KZ Organic</t>
+  </si>
+  <si>
+    <t>Revenue (₸ million)</t>
+  </si>
+  <si>
+    <t>Check: row 52 − row 23 (must be 0)</t>
+  </si>
+  <si>
+    <t>Provision / Avg Net Loan Portfolio</t>
+  </si>
+  <si>
+    <t>Fintech interest expense / Avg Net Loan Portfolio</t>
+  </si>
+  <si>
+    <t>2025 replay inputs</t>
+  </si>
+  <si>
+    <t>Payments total revenue / TPV (blended, incl. interest)</t>
+  </si>
+  <si>
+    <t>Marketplace blended revenue / GMV (incl. 1P, not a take rate)</t>
+  </si>
+  <si>
+    <t>Fintech revenue / TFV (legacy ratio, not a yield)</t>
+  </si>
+  <si>
+    <t>TFV-to-portfolio conversion (x) = TFV ÷ Avg Net Loan Portfolio</t>
+  </si>
+  <si>
+    <t>Fee revenue share of Fintech revenue (ex other gains), %</t>
+  </si>
+  <si>
+    <t>Bridge: change in blended revenue / GMV, 2024 → 2025 (bps)</t>
+  </si>
+  <si>
+    <t>Fee revenue (take rate effect)</t>
+  </si>
+  <si>
+    <t>Segment net income − consolidated net income</t>
+  </si>
+  <si>
+    <t>Payments: fee + interest − segment revenue</t>
+  </si>
+  <si>
+    <t>Marketplace: fee + retail + interest + gains − segment revenue</t>
+  </si>
+  <si>
+    <t>Türkiye components − Türkiye revenue by geography</t>
+  </si>
+  <si>
+    <t>Geography revenue − rewards − consolidated revenue</t>
+  </si>
+  <si>
+    <t>Overall status</t>
+  </si>
+  <si>
+    <t>Fintech: interest + fee + other − segment revenue</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>YoY vs 2025 replay base (incl. add-back of Fintech other losses)</t>
+  </si>
+  <si>
+    <t>Check: bridge total − change in row 52 (must be 0)</t>
+  </si>
+  <si>
+    <t>bps</t>
+  </si>
+  <si>
+    <t>1P retail (KZ)</t>
+  </si>
+  <si>
+    <t>Interest on merchant balances (KZ)</t>
+  </si>
+  <si>
+    <t>Other gains (KZ)</t>
+  </si>
+  <si>
+    <t>Total change in blended revenue / GMV (bps)</t>
   </si>
 </sst>
 </file>
@@ -469,10 +502,10 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="0.000"/>
-    <numFmt numFmtId="177" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -500,40 +533,21 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Inter Tight"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Inter Tight Medium"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Inter Tight"/>
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -559,21 +573,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -616,22 +621,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -640,24 +635,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -680,19 +669,47 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -748,36 +765,15 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-              </a:rPr>
-              <a:t>Hepsiburada Acquisition Drove 83% of </a:t>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Hepsiburada Consolidation Drove 86% </a:t>
             </a:r>
             <a:br>
-              <a:rPr lang="ru-RU" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-              </a:rPr>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
             </a:br>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-              </a:rPr>
-              <a:t>Marketplace Revenue Growth in 2025</a:t>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>of Marketplace Revenue Growth in 2025</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" sz="1200">
               <a:solidFill>
@@ -832,7 +828,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2025 KZ Organic</c:v>
+                  <c:v>KZ Organic</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -923,13 +919,13 @@
             <c:numRef>
               <c:f>Analysis!$J$31:$J$32</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>732943</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>936118</c:v>
+                  <c:v>899880</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1047,13 +1043,13 @@
             <c:numRef>
               <c:f>Analysis!$K$31:$K$32</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="General">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>995354</c:v>
+                  <c:v>1031592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1136,7 +1132,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1244,47 +1240,51 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter Tight" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter Tight" pitchFamily="2" charset="0"/>
-                <a:cs typeface="Inter Tight" pitchFamily="2" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+                <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+                <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
               </a:rPr>
-              <a:t>2026E KZ Ecosystem Revenue Resilience </a:t>
+              <a:t>2026E KZ Segment Revenue </a:t>
             </a:r>
-            <a:br>
-              <a:rPr lang="ru-RU" sz="1200">
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-              </a:rPr>
-            </a:br>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
               </a:rPr>
-              <a:t>Across Bear, Base, and Bull Scenarios</a:t>
+              <a:t>and Net Income by Scenario</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1301,13 +1301,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:latin typeface="Inter Tight" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter Tight" pitchFamily="2" charset="0"/>
-              <a:cs typeface="Inter Tight" pitchFamily="2" charset="0"/>
+              <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="ru-KZ"/>
@@ -1325,22 +1325,11 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$B$40</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total 2026E KZ segment revenue (pre-eliminations)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Revenue</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="65000"/>
-                <a:lumOff val="35000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1348,25 +1337,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="E31937"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-90CB-4CFD-9961-C7CB9FD3396F}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1425,35 +1395,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$C$30:$E$30</c:f>
+              <c:f>Analysis!$C$66:$E$66</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Bear Case</c:v>
+                  <c:v>Bear</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Base Case</c:v>
+                  <c:v>Base</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Bull Case</c:v>
+                  <c:v>Bull</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$C$40:$E$40</c:f>
+              <c:f>Analysis!$C$83:$E$83</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3286656.1300000004</c:v>
+                  <c:v>3152135.8883783785</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3576801.6849999996</c:v>
+                  <c:v>3545776.6449999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3894032.8200000003</c:v>
+                  <c:v>3832111.14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1461,6 +1431,121 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-90CB-4CFD-9961-C7CB9FD3396F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Net Income</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Inter Tight" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="Inter Tight" pitchFamily="2" charset="0"/>
+                    <a:cs typeface="Inter Tight" pitchFamily="2" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-KZ"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$C$66:$E$66</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Bear</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Base</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bull</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$C$98:$E$98</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>742930.57949189201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1329244.4169983333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1737159.3540000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-71C0-4BCF-9151-A476DF2A5272}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1652,43 +1737,27 @@
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="Inter Tight" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter Tight" pitchFamily="2" charset="0"/>
-                <a:cs typeface="Inter Tight" pitchFamily="2" charset="0"/>
+                <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+                <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+                <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
                 <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
               </a:rPr>
-              <a:t>Top-Line Expansion vs. Net Margin Compression </a:t>
+              <a:t>Türkiye Consolidation Explains ~3/4 of the Margin Drop</a:t>
             </a:r>
-            <a:br>
-              <a:rPr lang="ru-RU" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-              </a:rPr>
-            </a:br>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-                <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
-              </a:rPr>
-              <a:t>(The Cost of Transitioning to 1P Retail)</a:t>
-            </a:r>
+            <a:endParaRPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1709,9 +1778,9 @@
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:latin typeface="Inter Tight" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Inter Tight" pitchFamily="2" charset="0"/>
-              <a:cs typeface="Inter Tight" pitchFamily="2" charset="0"/>
+              <a:latin typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
+              <a:cs typeface="Inter Tight SemiBold" pitchFamily="2" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="ru-KZ"/>
@@ -1734,7 +1803,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Revenue (Billion)</c:v>
+                  <c:v>Revenue (₸ million)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1808,30 +1877,35 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
-              <c:f>Analysis!$I$35:$I$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+            <c:strRef>
+              <c:f>Analysis!$I$35:$I$37</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2024</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2025</c:v>
+                  <c:v>2025 ex-Türkiye</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+                <c:pt idx="2">
+                  <c:v>2025 Group</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$J$35:$J$36</c:f>
+              <c:f>Analysis!$J$35:$J$37</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)">
                   <c:v>2532156</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>3027244</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)">
                   <c:v>4046074</c:v>
                 </c:pt>
               </c:numCache>
@@ -1852,7 +1926,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:gapWidth val="87"/>
         <c:axId val="215252911"/>
         <c:axId val="215253743"/>
       </c:barChart>
@@ -1955,30 +2029,35 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
-              <c:f>Analysis!$I$35:$I$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+            <c:strRef>
+              <c:f>Analysis!$I$35:$I$37</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>2024</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2025</c:v>
+                  <c:v>2025 ex-Türkiye</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+                <c:pt idx="2">
+                  <c:v>2025 Group</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$K$35:$K$36</c:f>
+              <c:f>Analysis!$K$35:$K$37</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>0.41736528081208268</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.382285339404422</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.26388716568209086</c:v>
                 </c:pt>
               </c:numCache>
@@ -4318,7 +4397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A88866-A1AE-4376-A066-EACDBAE1C6EE}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="B2:E60"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.640625" customWidth="1"/>
@@ -4328,17 +4407,12 @@
     <col min="6" max="6" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:5" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>13</v>
       </c>
       <c r="D2" s="14">
         <v>2024</v>
@@ -4347,12 +4421,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B3" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4">
         <v>2532156</v>
@@ -4361,12 +4435,12 @@
         <v>4046074</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B4" s="13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4">
         <v>587097</v>
@@ -4375,12 +4449,12 @@
         <v>658726</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4">
         <v>732943</v>
@@ -4389,12 +4463,12 @@
         <v>1931472</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B6" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="4">
         <v>1281827</v>
@@ -4403,12 +4477,12 @@
         <v>1542934</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4">
         <v>1056834</v>
@@ -4417,12 +4491,12 @@
         <v>1067707</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="4">
         <v>37229000</v>
@@ -4431,12 +4505,12 @@
         <v>44219000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="4">
         <v>5975000</v>
@@ -4445,12 +4519,12 @@
         <v>6657000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="4">
         <v>10305000</v>
@@ -4459,13 +4533,13 @@
         <v>11652000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
-    <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="13" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
         <v>13.6</v>
@@ -4474,12 +4548,12 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1">
         <v>8.1</v>
@@ -4488,12 +4562,12 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1">
         <v>6.4</v>
@@ -4502,13 +4576,13 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -4518,12 +4592,12 @@
         <v>1031592</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="18">
         <v>303858</v>
@@ -4532,277 +4606,515 @@
         <v>1179141</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B21" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="22">
+        <v>13</v>
+      </c>
+      <c r="D21" s="20">
         <v>2586381</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="20">
         <v>3070369</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B22" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="28">
+        <v>13</v>
+      </c>
+      <c r="D22" s="24">
         <v>0</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="20">
         <v>1031592</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B23" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="22">
+        <v>13</v>
+      </c>
+      <c r="D23" s="20">
         <v>54225</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="20">
         <v>55887</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B25" s="29" t="s">
-        <v>73</v>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B25" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="42">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="36">
         <v>458953</v>
       </c>
-      <c r="E26" s="42">
+      <c r="E26" s="36">
         <v>510763</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="42">
+        <v>57</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="36">
         <v>128144</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E27" s="36">
         <v>147963</v>
       </c>
-      <c r="F27" s="40">
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="36">
+        <v>562283</v>
+      </c>
+      <c r="E28" s="36">
+        <v>974269</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="37">
+        <v>0</v>
+      </c>
+      <c r="E29" s="36">
+        <v>302921</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="36">
+        <v>5797000</v>
+      </c>
+      <c r="E30" s="36">
+        <v>6423000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="36">
+        <v>178000</v>
+      </c>
+      <c r="E31" s="36">
+        <v>234000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="36">
+        <v>163134</v>
+      </c>
+      <c r="E32" s="36">
+        <v>850127</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="37">
+        <v>0</v>
+      </c>
+      <c r="E33" s="36">
+        <v>638164</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="36">
+        <v>6304</v>
+      </c>
+      <c r="E34" s="36">
+        <v>69886</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="37">
+        <v>0</v>
+      </c>
+      <c r="E35" s="36">
+        <v>54269</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="36">
+        <v>1222</v>
+      </c>
+      <c r="E36" s="36">
+        <v>37190</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="37">
+        <v>0</v>
+      </c>
+      <c r="E37" s="36">
+        <v>36238</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="36">
+        <v>955528</v>
+      </c>
+      <c r="E38" s="36">
+        <v>1383465</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="36">
+        <v>316292</v>
+      </c>
+      <c r="E39" s="36">
+        <v>178409</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="36">
+        <v>10007</v>
+      </c>
+      <c r="E40" s="36">
+        <v>-18940</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="36">
+        <v>4895000</v>
+      </c>
+      <c r="E41" s="36">
+        <v>6415000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="33">
+        <v>0.24</v>
+      </c>
+      <c r="E42" s="33">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B43" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E43">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="36">
+        <v>381607</v>
+      </c>
+      <c r="E44" s="36">
+        <v>433001</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B45" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="36">
+        <v>348400</v>
+      </c>
+      <c r="E45" s="36">
+        <v>279773</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B46" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="36">
+        <v>326827</v>
+      </c>
+      <c r="E46" s="36">
+        <v>354933</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="42" x14ac:dyDescent="0.5">
+      <c r="B47" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="37">
+        <v>0</v>
+      </c>
+      <c r="E47" s="36">
+        <v>-93018</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B48" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="36">
+        <v>616116</v>
+      </c>
+      <c r="E48" s="36">
+        <v>908698</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="36">
+        <v>113957</v>
+      </c>
+      <c r="E49" s="36">
+        <v>161651</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="37">
+        <v>0</v>
+      </c>
+      <c r="E50" s="36">
+        <v>-89564</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="37">
+        <v>0</v>
+      </c>
+      <c r="E51" s="36">
+        <v>1018830</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B53" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+    </row>
+    <row r="54" spans="2:5" ht="42" x14ac:dyDescent="0.5">
+      <c r="B54" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D54" s="53">
+        <f>D44+D45+D46-D7</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="53">
+        <f>E44+E45+E46-E7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B55" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" s="34">
+        <f>D26+D27-D4</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="34">
         <f>E26+E27-E4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="42">
-        <v>562283</v>
-      </c>
-      <c r="E28" s="42">
-        <v>974269</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" s="43">
+    <row r="56" spans="2:5" ht="42" x14ac:dyDescent="0.5">
+      <c r="B56" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D56" s="53">
+        <f>D28+D32+D34+D36-D5</f>
         <v>0</v>
       </c>
-      <c r="E29" s="42">
-        <v>302921</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" s="42">
-        <v>5797000</v>
-      </c>
-      <c r="E30" s="42">
-        <v>6423000</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B31" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="42">
-        <v>178000</v>
-      </c>
-      <c r="E31" s="42">
-        <v>234000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B32" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="42">
-        <v>163134</v>
-      </c>
-      <c r="E32" s="42">
-        <v>850127</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" s="43">
-        <v>0</v>
-      </c>
-      <c r="E33" s="42">
-        <v>638164</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="42">
-        <v>6304</v>
-      </c>
-      <c r="E34" s="42">
-        <v>69886</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B35" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="43">
-        <v>0</v>
-      </c>
-      <c r="E35" s="42">
-        <v>54269</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B36" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="42">
-        <v>1222</v>
-      </c>
-      <c r="E36" s="42">
-        <v>37190</v>
-      </c>
-      <c r="F36" s="16">
+      <c r="E56" s="53">
         <f>E28+E32+E34+E36-E5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" s="43">
+    <row r="57" spans="2:5" ht="42" x14ac:dyDescent="0.5">
+      <c r="B57" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="55">
+        <f>D38+D39+D40-D6</f>
         <v>0</v>
       </c>
-      <c r="E37" s="42">
-        <v>36238</v>
-      </c>
-      <c r="F37" s="16">
-        <f>D28+D32+D34+D36-D5</f>
+      <c r="E57" s="55">
+        <f>E38+E39+E40-E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B38" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="42">
-        <v>955528</v>
-      </c>
-      <c r="E38" s="42">
-        <v>1383465</v>
-      </c>
-      <c r="F38" s="40">
+    <row r="58" spans="2:5" ht="42" x14ac:dyDescent="0.5">
+      <c r="B58" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D58" s="54"/>
+      <c r="E58" s="34">
         <f>E29+E33+E35+E37-E22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B39" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="42">
-        <v>316292</v>
-      </c>
-      <c r="E39" s="42">
-        <v>178409</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B40" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="42">
-        <v>10007</v>
-      </c>
-      <c r="E40" s="42">
-        <v>-18940</v>
-      </c>
-      <c r="F40" s="16">
-        <f>E38+E39+E40-E6</f>
+    <row r="59" spans="2:5" ht="42" x14ac:dyDescent="0.5">
+      <c r="B59" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" s="53">
+        <f>D21+D22-D23-D3</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B41" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="42">
-        <v>4895000</v>
-      </c>
-      <c r="E41" s="42">
-        <v>6415000</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B42" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="39">
-        <v>0.24</v>
-      </c>
-      <c r="E42" s="39">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B43" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="E59" s="53">
+        <f>E21+E22-E23-E3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B60" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D60" s="52" t="str">
+        <f>IF(SUMPRODUCT(ABS(D54:E59))&lt;0.5,"OK","ERROR")</f>
+        <v>OK</v>
+      </c>
+      <c r="E60" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4812,18 +5124,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B0785C-78F9-4626-9FC5-2C19389EC9FB}">
-  <dimension ref="B2:K118"/>
+  <dimension ref="B2:K103"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.640625" customWidth="1"/>
-    <col min="2" max="2" width="29.5" customWidth="1"/>
+    <col min="2" max="2" width="37.2109375" customWidth="1"/>
     <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.0703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.2109375" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
     <col min="9" max="9" width="15.2109375" customWidth="1"/>
-    <col min="10" max="10" width="14.640625" customWidth="1"/>
-    <col min="11" max="11" width="17.0703125" customWidth="1"/>
+    <col min="10" max="10" width="16.0703125" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -4834,17 +5146,17 @@
         <v>2025</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B3" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5">
         <f>(Raw_Data!E3 / Raw_Data!D3) - 1</f>
@@ -4853,7 +5165,7 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B5" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5">
         <f>(Raw_Data!E4 / Raw_Data!D4) - 1</f>
@@ -4862,7 +5174,7 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B6" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5">
         <f>(Raw_Data!E5 / Raw_Data!D5) - 1</f>
@@ -4871,7 +5183,7 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B7" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="5">
         <f>(Raw_Data!E6 / Raw_Data!D6) - 1</f>
@@ -4880,7 +5192,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B8" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="11">
@@ -4890,12 +5202,12 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B10" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5">
         <f>Raw_Data!D4 / SUM(Raw_Data!D$4:D$6)</f>
@@ -4908,7 +5220,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5">
         <f>Raw_Data!D5 / SUM(Raw_Data!D$4:D$6)</f>
@@ -4921,7 +5233,7 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B13" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="11">
         <f>Raw_Data!D6 / SUM(Raw_Data!D$4:D$6)</f>
@@ -4934,7 +5246,7 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B15" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="6">
         <f>Raw_Data!D7 / Raw_Data!D3</f>
@@ -4947,12 +5259,12 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B17" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B18" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="16">
         <f>Raw_Data!D5</f>
@@ -4969,7 +5281,7 @@
     </row>
     <row r="19" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B19" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="5">
         <f>Raw_Data!E17 / (Raw_Data!E5 - Raw_Data!D5)</f>
@@ -4979,12 +5291,12 @@
     <row r="20" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
     <row r="21" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B21" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B22" s="12" t="s">
-        <v>29</v>
+      <c r="B22" t="s">
+        <v>132</v>
       </c>
       <c r="C22" s="17">
         <f>Raw_Data!D4 / Raw_Data!D9</f>
@@ -4996,8 +5308,8 @@
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B23" s="12" t="s">
-        <v>55</v>
+      <c r="B23" t="s">
+        <v>133</v>
       </c>
       <c r="C23" s="5">
         <f>Raw_Data!D5 / Raw_Data!D10</f>
@@ -5010,7 +5322,7 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B24" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C24" s="18">
         <f>Raw_Data!D10 / Raw_Data!D14</f>
@@ -5023,7 +5335,7 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B25" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="C25" s="5">
         <f>Raw_Data!D6 / Raw_Data!D11</f>
@@ -5036,7 +5348,7 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C26" s="18">
         <f>Raw_Data!D4 / Raw_Data!D13</f>
@@ -5049,7 +5361,7 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B27" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C27" s="18">
         <f>C18 / Raw_Data!D14</f>
@@ -5062,7 +5374,7 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C28" s="18">
         <f>Raw_Data!D6 / Raw_Data!D15</f>
@@ -5073,125 +5385,127 @@
         <v>244910.15873015873</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B30" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>54</v>
-      </c>
+    <row r="30" spans="2:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="30">
+        <v>2024</v>
+      </c>
+      <c r="D30" s="30">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="26"/>
       <c r="I30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="C31" s="28">
+        <f>Raw_Data!D4</f>
+        <v>587097</v>
+      </c>
+      <c r="D31" s="28">
+        <f>Raw_Data!E4</f>
+        <v>658726</v>
+      </c>
+      <c r="E31" s="26"/>
+      <c r="I31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="16">
+        <f>C18</f>
+        <v>732943</v>
+      </c>
+      <c r="K31">
+        <f>Raw_Data!D17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B32" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="28">
+        <f>Raw_Data!D5</f>
+        <v>732943</v>
+      </c>
+      <c r="D32" s="28">
+        <f>Raw_Data!E5</f>
+        <v>1931472</v>
+      </c>
+      <c r="E32" s="26"/>
+      <c r="I32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J32" s="16">
+        <f>D18</f>
+        <v>899880</v>
+      </c>
+      <c r="K32" s="18">
+        <f>Raw_Data!E17</f>
+        <v>1031592</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B33" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="K30" s="7" t="s">
+      <c r="C33" s="28">
+        <f>Raw_Data!D6</f>
+        <v>1281827</v>
+      </c>
+      <c r="D33" s="28">
+        <f>Raw_Data!E6</f>
+        <v>1542934</v>
+      </c>
+      <c r="E33" s="26"/>
+    </row>
+    <row r="34" spans="2:11" ht="42" x14ac:dyDescent="0.5">
+      <c r="B34" s="27" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B31" s="12" t="s">
+      <c r="C34" s="28">
+        <f>SUM(C31:C33)</f>
+        <v>2601867</v>
+      </c>
+      <c r="D34" s="28">
+        <f>SUM(D31:D33)</f>
+        <v>4133132</v>
+      </c>
+      <c r="E34" s="26"/>
+      <c r="I34" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J31">
-        <v>732943</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B32" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="17">
-        <v>1.4500000000000001E-2</v>
-      </c>
-      <c r="D32" s="17">
-        <v>1.49E-2</v>
-      </c>
-      <c r="E32" s="17">
-        <v>1.52E-2</v>
-      </c>
-      <c r="I32" s="7" t="s">
+      <c r="J34" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B35" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="J32">
-        <v>936118</v>
-      </c>
-      <c r="K32">
-        <v>995354</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B33" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B34" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="5">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0.155</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="K34" s="25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B35" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="D35" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="E35" s="5">
-        <v>0.18</v>
-      </c>
+      <c r="C35" s="44">
+        <f>-(C34-(Raw_Data!D21+Raw_Data!D22))</f>
+        <v>-15486</v>
+      </c>
+      <c r="D35" s="44">
+        <f>-(D34-(Raw_Data!E21+Raw_Data!E22))</f>
+        <v>-31171</v>
+      </c>
+      <c r="E35" s="26"/>
       <c r="I35" s="8">
         <v>2024</v>
       </c>
@@ -5199,1047 +5513,941 @@
         <f>Raw_Data!D3</f>
         <v>2532156</v>
       </c>
-      <c r="K35" s="24">
+      <c r="K35" s="21">
         <f>C15</f>
         <v>0.41736528081208268</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B36" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="5">
-        <v>0.128</v>
-      </c>
-      <c r="D36" s="5">
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="E36" s="5">
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="I36" s="8">
-        <v>2025</v>
-      </c>
-      <c r="J36" s="18">
+      <c r="B36" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="44">
+        <f>-Raw_Data!D23</f>
+        <v>-54225</v>
+      </c>
+      <c r="D36" s="44">
+        <f>-Raw_Data!E23</f>
+        <v>-55887</v>
+      </c>
+      <c r="E36" s="26"/>
+      <c r="I36" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="J36" s="16">
+        <f>Raw_Data!$E$3-Raw_Data!$E$51</f>
+        <v>3027244</v>
+      </c>
+      <c r="K36" s="5">
+        <f>F102</f>
+        <v>0.382285339404422</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B37" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="28">
+        <f>C34+C35+C36</f>
+        <v>2532156</v>
+      </c>
+      <c r="D37" s="28">
+        <f>D34+D35+D36</f>
+        <v>4046074</v>
+      </c>
+      <c r="E37" s="26"/>
+      <c r="I37" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="J37" s="18">
         <f>Raw_Data!E3</f>
         <v>4046074</v>
       </c>
-      <c r="K36" s="24">
-        <f>D15</f>
+      <c r="K37" s="5">
+        <f>F101</f>
         <v>0.26388716568209086</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B37" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="21">
-        <f>Raw_Data!$E9*(1+C31)*C32</f>
-        <v>705293.05000000016</v>
-      </c>
-      <c r="D37" s="21">
-        <f>Raw_Data!$E9*(1+D31)*D32</f>
-        <v>757692.56499999994</v>
-      </c>
-      <c r="E37" s="21">
-        <f>Raw_Data!$E9*(1+E31)*E32</f>
-        <v>806554.56</v>
-      </c>
-    </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B38" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="22">
-        <f>Raw_Data!$E10*(1+C33)*C34</f>
-        <v>970590.60000000021</v>
-      </c>
-      <c r="D38" s="22">
-        <f>Raw_Data!$E10*(1+D33)*D34</f>
-        <v>1081096.8</v>
-      </c>
-      <c r="E38" s="22">
-        <f>Raw_Data!$E10*(1+E33)*E34</f>
-        <v>1217565.3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B39" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="22">
-        <f>Raw_Data!$E11*(1+C35)*C36</f>
-        <v>1610772.48</v>
-      </c>
-      <c r="D39" s="22">
-        <f>Raw_Data!$E11*(1+D35)*D36</f>
-        <v>1738012.3199999998</v>
-      </c>
-      <c r="E39" s="22">
-        <f>Raw_Data!$E11*(1+E35)*E36</f>
-        <v>1869912.9600000002</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" ht="42" x14ac:dyDescent="0.5">
-      <c r="B40" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="36">
-        <f>SUM(C37:C39)</f>
-        <v>3286656.1300000004</v>
-      </c>
-      <c r="D40" s="36">
-        <f>SUM(D37:D39)</f>
-        <v>3576801.6849999996</v>
-      </c>
-      <c r="E40" s="36">
-        <f>SUM(E37:E39)</f>
-        <v>3894032.8200000003</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="34">
-        <v>2024</v>
-      </c>
-      <c r="D42" s="34">
-        <v>2025</v>
-      </c>
-      <c r="E42" s="30"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B43" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="32">
-        <f>Raw_Data!D4</f>
-        <v>587097</v>
-      </c>
-      <c r="D43" s="32">
-        <f>Raw_Data!E4</f>
-        <v>658726</v>
-      </c>
-      <c r="E43" s="30"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B44" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="32">
-        <f>Raw_Data!D5</f>
-        <v>732943</v>
-      </c>
-      <c r="D44" s="32">
-        <f>Raw_Data!E5</f>
-        <v>1931472</v>
-      </c>
-      <c r="E44" s="30"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B45" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="32">
-        <f>Raw_Data!D6</f>
-        <v>1281827</v>
-      </c>
-      <c r="D45" s="32">
-        <f>Raw_Data!E6</f>
-        <v>1542934</v>
-      </c>
-      <c r="E45" s="30"/>
-    </row>
-    <row r="46" spans="2:11" ht="42" x14ac:dyDescent="0.5">
-      <c r="B46" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="32">
-        <f>SUM(C43:C45)</f>
-        <v>2601867</v>
-      </c>
-      <c r="D46" s="32">
-        <f>SUM(D43:D45)</f>
-        <v>4133132</v>
-      </c>
-      <c r="E46" s="30"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B47" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="51">
-        <f>-(C46-(Raw_Data!D21+Raw_Data!D22))</f>
-        <v>-15486</v>
-      </c>
-      <c r="D47" s="51">
-        <f>-(D46-(Raw_Data!E21+Raw_Data!E22))</f>
-        <v>-31171</v>
-      </c>
-      <c r="E47" s="30"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.5">
-      <c r="B48" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="51">
-        <f>-Raw_Data!D23</f>
-        <v>-54225</v>
-      </c>
-      <c r="D48" s="51">
-        <f>-Raw_Data!E23</f>
-        <v>-55887</v>
-      </c>
-      <c r="E48" s="30"/>
-    </row>
-    <row r="49" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B49" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="32">
-        <f>C46+C47+C48</f>
-        <v>2532156</v>
-      </c>
-      <c r="D49" s="32">
-        <f>D46+D47+D48</f>
-        <v>4046074</v>
-      </c>
-      <c r="E49" s="30"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B50" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="32">
+      <c r="B38" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="28">
         <f>Raw_Data!D3</f>
         <v>2532156</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D38" s="28">
         <f>Raw_Data!E3</f>
         <v>4046074</v>
       </c>
-      <c r="E50" s="30"/>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B51" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="32">
-        <f>C49-C50</f>
+      <c r="E38" s="26"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B39" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="28">
+        <f>C37-C38</f>
         <v>0</v>
       </c>
-      <c r="D51" s="32">
-        <f>D49-D50</f>
+      <c r="D39" s="28">
+        <f>D37-D38</f>
         <v>0</v>
       </c>
-      <c r="E51" s="30"/>
-    </row>
-    <row r="52" spans="2:5" ht="42" x14ac:dyDescent="0.5">
-      <c r="B52" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="33">
-        <f>-(C47+C48)/C46</f>
+      <c r="E39" s="26"/>
+    </row>
+    <row r="40" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B40" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="29">
+        <f>-(C35+C36)/C34</f>
         <v>2.6792683868929502E-2</v>
       </c>
-      <c r="D52" s="33">
-        <f>-(D47+D48)/D46</f>
+      <c r="D40" s="29">
+        <f>-(D35+D36)/D34</f>
         <v>2.1063445348466974E-2</v>
       </c>
-      <c r="E52" s="30"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B58" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58" s="16">
+      <c r="E40" s="26"/>
+    </row>
+    <row r="42" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B43" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="16">
         <f>Raw_Data!E4+(Raw_Data!E5-Raw_Data!E17)+Raw_Data!E6</f>
         <v>3101540</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B62" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B63" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" s="17">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B46" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B47" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="17">
         <f>Raw_Data!D26/Raw_Data!D9</f>
         <v>1.232783582690913E-2</v>
       </c>
-      <c r="D63" s="17">
+      <c r="D47" s="17">
         <f>Raw_Data!E26/Raw_Data!E9</f>
         <v>1.1550758723625591E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B64" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C64" s="18">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.5">
+      <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="18">
         <f>Raw_Data!D27</f>
         <v>128144</v>
       </c>
-      <c r="D64" s="18">
+      <c r="D48" s="18">
         <f>Raw_Data!E27</f>
         <v>147963</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B65" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" s="18">
+    <row r="49" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B49" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="18">
         <f>Raw_Data!D28-Raw_Data!D29</f>
         <v>562283</v>
       </c>
-      <c r="D65" s="18">
+      <c r="D49" s="18">
         <f>Raw_Data!E28-Raw_Data!E29</f>
         <v>671348</v>
       </c>
     </row>
-    <row r="66" spans="2:4" ht="42" x14ac:dyDescent="0.5">
-      <c r="B66" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C66" s="44">
-        <f>C65/Raw_Data!D30</f>
+    <row r="50" spans="2:4" ht="42" x14ac:dyDescent="0.5">
+      <c r="B50" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="38">
+        <f>C49/Raw_Data!D30</f>
         <v>9.6995514921511122E-2</v>
       </c>
-      <c r="D66" s="44">
-        <f>D65/Raw_Data!E30</f>
+      <c r="D50" s="38">
+        <f>D49/Raw_Data!E30</f>
         <v>0.10452249727541647</v>
       </c>
     </row>
-    <row r="67" spans="2:4" ht="42" x14ac:dyDescent="0.5">
-      <c r="B67" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C67" s="45">
+    <row r="51" spans="2:4" ht="42" x14ac:dyDescent="0.5">
+      <c r="B51" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="39">
         <f>(Raw_Data!D32-Raw_Data!D33)+(Raw_Data!D34-Raw_Data!D35)+(Raw_Data!D36-Raw_Data!D37)</f>
         <v>170660</v>
       </c>
-      <c r="D67" s="45">
+      <c r="D51" s="39">
         <f>(Raw_Data!E32-Raw_Data!E33)+(Raw_Data!E34-Raw_Data!E35)+(Raw_Data!E36-Raw_Data!E37)</f>
         <v>228532</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B68" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C68" s="17">
-        <f>(C65+C67)/Raw_Data!D10</f>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B52" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="17">
+        <f>(C49+C51)/Raw_Data!D10</f>
         <v>0.12266828451882845</v>
       </c>
-      <c r="D68" s="17">
-        <f>(D65+D67)/Raw_Data!E10</f>
+      <c r="D52" s="17">
+        <f>(D49+D51)/Raw_Data!E10</f>
         <v>0.13517800811176206</v>
       </c>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B69" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" s="18">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" s="18">
         <f>Raw_Data!D38+Raw_Data!D39</f>
         <v>1271820</v>
       </c>
-      <c r="D69" s="18">
+      <c r="D53" s="18">
         <f>Raw_Data!E38+Raw_Data!E39</f>
         <v>1561874</v>
       </c>
     </row>
-    <row r="70" spans="2:4" ht="42" x14ac:dyDescent="0.5">
-      <c r="B70" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C70" s="44">
-        <f>C69/Raw_Data!D41</f>
+    <row r="54" spans="2:4" ht="42" x14ac:dyDescent="0.5">
+      <c r="B54" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="38">
+        <f>C53/Raw_Data!D41</f>
         <v>0.2598202247191011</v>
       </c>
-      <c r="D70" s="44">
-        <f>D69/Raw_Data!E41</f>
+      <c r="D54" s="38">
+        <f>D53/Raw_Data!E41</f>
         <v>0.24347217459080281</v>
       </c>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B71" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C71" s="46">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B55" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" s="40">
         <f>Raw_Data!D11/Raw_Data!D41</f>
         <v>2.105209397344229</v>
       </c>
-      <c r="D71" s="46">
+      <c r="D55" s="40">
         <f>Raw_Data!E11/Raw_Data!E41</f>
         <v>1.8163678877630554</v>
       </c>
     </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B72" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C72" s="5">
-        <f>Raw_Data!D39/C69</f>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="5">
+        <f>Raw_Data!D39/C53</f>
         <v>0.24869242502869904</v>
       </c>
-      <c r="D72" s="5">
-        <f>Raw_Data!E39/D69</f>
+      <c r="D56" s="5">
+        <f>Raw_Data!E39/D53</f>
         <v>0.11422752411526153</v>
       </c>
     </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B73" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C73" s="47">
-        <f>C68-C23</f>
+    <row r="57" spans="2:4" s="51" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B57" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="50">
+        <f>C52-C23</f>
         <v>0</v>
       </c>
-      <c r="D73" s="47">
-        <f>D68-D23</f>
+      <c r="D57" s="50">
+        <f>D52-D23</f>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B75" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D75" s="48">
-        <f>(D65/Raw_Data!E10-C65/Raw_Data!D10)*10000</f>
+    <row r="58" spans="2:4" ht="42" x14ac:dyDescent="0.5">
+      <c r="B58" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58" s="56" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B59" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59" s="41">
+        <f>(D49/Raw_Data!E10-C49/Raw_Data!D10)*10000</f>
         <v>67.424888012304066</v>
       </c>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B76" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D76" s="48">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B60" t="s">
+        <v>150</v>
+      </c>
+      <c r="D60" s="41">
         <f>(Raw_Data!E32-Raw_Data!E33)/Raw_Data!E10*10000 - (Raw_Data!D32-Raw_Data!D33)/Raw_Data!D10*10000</f>
         <v>45.378573911250783</v>
       </c>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B77" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D77" s="48">
+    <row r="61" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B61" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" s="41">
         <f>((Raw_Data!E34-Raw_Data!E35)/Raw_Data!E10 - (Raw_Data!D34-Raw_Data!D35)/Raw_Data!D10)*10000</f>
         <v>12.908888683570259</v>
       </c>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B78" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D78" s="48">
+    <row r="62" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B62" t="s">
+        <v>152</v>
+      </c>
+      <c r="D62" s="41">
         <f>((Raw_Data!E36-Raw_Data!E37)/Raw_Data!E10 - (Raw_Data!D36-Raw_Data!D37)/Raw_Data!D10)*10000</f>
         <v>-0.61511467778907036</v>
       </c>
     </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B79" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D79" s="48">
-        <f>SUM(D75:D78)</f>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B63" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D63" s="41">
+        <f>SUM(D59:D62)</f>
         <v>125.09723592933604</v>
       </c>
     </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64">
+        <f>D63-(D52-C52)*10000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="C66" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="D67" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="E67" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="F67" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="43">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D68" s="43">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="E68" s="43">
+        <v>1.155E-2</v>
+      </c>
+      <c r="F68" s="43">
+        <f>D47</f>
+        <v>1.1550758723625591E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B69" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" s="32">
+        <v>-0.1</v>
+      </c>
+      <c r="D69" s="32">
+        <v>0.08</v>
+      </c>
+      <c r="E69" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="F69" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B70" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="D70" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="E70" s="32">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F70" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B71" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="17">
+        <v>0.1045</v>
+      </c>
+      <c r="D71" s="17">
+        <v>0.109</v>
+      </c>
+      <c r="E71" s="17">
+        <v>0.112</v>
+      </c>
+      <c r="F71" s="17">
+        <f>D50</f>
+        <v>0.10452249727541647</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B72" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="D72" s="32">
+        <v>0.25</v>
+      </c>
+      <c r="E72" s="32">
+        <v>0.35</v>
+      </c>
+      <c r="F72" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B73" t="s">
+        <v>86</v>
+      </c>
+      <c r="C73" s="32">
+        <v>0.05</v>
+      </c>
+      <c r="D73" s="32">
+        <v>0.13</v>
+      </c>
+      <c r="E73" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="F73" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="35">
+        <v>1.85</v>
+      </c>
+      <c r="D74" s="35">
+        <v>1.8</v>
+      </c>
+      <c r="E74" s="35">
+        <v>1.75</v>
+      </c>
+      <c r="F74" s="35">
+        <f>D55</f>
+        <v>1.8163678877630554</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="E75" s="5">
+        <v>0.245</v>
+      </c>
+      <c r="F75" s="5">
+        <f>D54</f>
+        <v>0.24347217459080281</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B76" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="D76" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E76" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="F76" s="17">
+        <f>Raw_Data!E49/Raw_Data!E41</f>
+        <v>2.5198908807482462E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="18">
+        <f>Raw_Data!$E$9*(1+C67)*C68 + Raw_Data!$E$27*(1+C69)</f>
+        <v>668216.60000000009</v>
+      </c>
+      <c r="D78" s="18">
+        <f>Raw_Data!$E$9*(1+D67)*D68 + Raw_Data!$E$27*(1+D69)</f>
+        <v>734425.94499999995</v>
+      </c>
+      <c r="E78" s="18">
+        <f>Raw_Data!$E$9*(1+E67)*E68 + Raw_Data!$E$27*(1+E69)</f>
+        <v>778593.9</v>
+      </c>
+      <c r="F78" s="18">
+        <f>Raw_Data!$E$9*(1+F67)*F68 + Raw_Data!$E$27*(1+F69)</f>
+        <v>658726</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B79" t="s">
+        <v>95</v>
+      </c>
+      <c r="C79" s="18">
+        <f>Raw_Data!$E$30*(1+C70)*C71 + $D$51*(1+C72)</f>
+        <v>962860.90999999992</v>
+      </c>
+      <c r="D79" s="18">
+        <f>Raw_Data!$E$30*(1+D70)*D71 + $D$51*(1+D72)</f>
+        <v>1055782.7000000002</v>
+      </c>
+      <c r="E79" s="18">
+        <f>Raw_Data!$E$30*(1+E70)*E71 + $D$51*(1+E72)</f>
+        <v>1128606.8400000001</v>
+      </c>
+      <c r="F79" s="18">
+        <f>Raw_Data!$E$30*(1+F70)*F71 + $D$51*(1+F72)</f>
+        <v>899880</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B80" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" s="18">
+        <f>Raw_Data!$E$11*(1+C73)/C74*C75</f>
+        <v>1521058.3783783785</v>
+      </c>
+      <c r="D80" s="18">
+        <f>Raw_Data!$E$11*(1+D73)/D74*D75</f>
+        <v>1755567.9999999995</v>
+      </c>
+      <c r="E80" s="18">
+        <f>Raw_Data!$E$11*(1+E73)/E74*E75</f>
+        <v>1924910.4</v>
+      </c>
+      <c r="F80" s="18">
+        <f>Raw_Data!$E$11*(1+F73)/F74*F75</f>
+        <v>1561874</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B81" t="s">
+        <v>97</v>
+      </c>
+      <c r="C81" s="23">
+        <f>-(Raw_Data!$E$11*(1+C73)/C74)*C76</f>
+        <v>-330664.86486486485</v>
+      </c>
+      <c r="D81" s="23">
+        <f>-(Raw_Data!$E$11*(1+D73)/D74)*D76</f>
+        <v>-182871.66666666663</v>
+      </c>
+      <c r="E81" s="23">
+        <f>-(Raw_Data!$E$11*(1+E73)/E74)*E76</f>
+        <v>-157135.54285714286</v>
+      </c>
+      <c r="F81" s="23">
+        <f>-(Raw_Data!$E$11*(1+F73)/F74)*F76</f>
+        <v>-161651</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B82" t="s">
+        <v>98</v>
+      </c>
+      <c r="C82" s="18">
+        <f>C80+C81</f>
+        <v>1190393.5135135136</v>
+      </c>
+      <c r="D82" s="18">
+        <f>D80+D81</f>
+        <v>1572696.333333333</v>
+      </c>
+      <c r="E82" s="18">
+        <f>E80+E81</f>
+        <v>1767774.857142857</v>
+      </c>
+      <c r="F82" s="18">
+        <f>F80+F81</f>
+        <v>1400223</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B83" t="s">
+        <v>99</v>
+      </c>
+      <c r="C83" s="18">
+        <f>C78+C79+C80</f>
+        <v>3152135.8883783785</v>
+      </c>
+      <c r="D83" s="18">
+        <f>D78+D79+D80</f>
+        <v>3545776.6449999996</v>
+      </c>
+      <c r="E83" s="18">
+        <f>E78+E79+E80</f>
+        <v>3832111.14</v>
+      </c>
+      <c r="F83" s="18">
+        <f>F78+F79+F80</f>
+        <v>3120480</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B84" t="s">
+        <v>100</v>
+      </c>
+      <c r="C84" s="18">
+        <f>C78+C79+C82</f>
+        <v>2821471.0235135136</v>
+      </c>
+      <c r="D84" s="18">
+        <f>D78+D79+D82</f>
+        <v>3362904.978333333</v>
+      </c>
+      <c r="E84" s="18">
+        <f>E78+E79+E82</f>
+        <v>3674975.5971428575</v>
+      </c>
+      <c r="F84" s="18">
+        <f>F78+F79+F82</f>
+        <v>2958829</v>
+      </c>
+    </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="C85" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D85" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="E85" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="F85" s="49" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B86" t="s">
-        <v>107</v>
-      </c>
-      <c r="C86" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="D86" s="38">
-        <v>0.15</v>
-      </c>
-      <c r="E86" s="38">
-        <v>0.2</v>
-      </c>
-      <c r="F86" s="38">
+      <c r="B85" t="s">
+        <v>147</v>
+      </c>
+      <c r="C85" s="5">
+        <f>C83/$F$83-1</f>
+        <v>1.0144557368859441E-2</v>
+      </c>
+      <c r="D85" s="5">
+        <f>D83/$F$83-1</f>
+        <v>0.13629205923447651</v>
+      </c>
+      <c r="E85" s="5">
+        <f>E83/$F$83-1</f>
+        <v>0.22805181895093063</v>
+      </c>
+      <c r="F85" s="5">
+        <f>F83/$F$83-1</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B87" t="s">
-        <v>108</v>
-      </c>
-      <c r="C87" s="50">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="D87" s="50">
-        <v>1.1299999999999999E-2</v>
-      </c>
-      <c r="E87" s="50">
-        <v>1.155E-2</v>
-      </c>
-      <c r="F87" s="50">
-        <f>D63</f>
-        <v>1.1550758723625591E-2</v>
+      <c r="B87" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D87" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E87" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F87" s="22" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B88" t="s">
-        <v>109</v>
-      </c>
-      <c r="C88" s="38">
-        <v>-0.1</v>
-      </c>
-      <c r="D88" s="38">
-        <v>0.08</v>
-      </c>
-      <c r="E88" s="38">
-        <v>0.12</v>
-      </c>
-      <c r="F88" s="38">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="C88" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D88" s="5">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.68</v>
+      </c>
+      <c r="F88" s="17">
+        <f>Raw_Data!E44/F78</f>
+        <v>0.65733096917382949</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B89" t="s">
-        <v>110</v>
-      </c>
-      <c r="C89" s="38">
-        <v>0.06</v>
-      </c>
-      <c r="D89" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="E89" s="38">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F89" s="38">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="C89" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="D89" s="5">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="E89" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="F89" s="17">
+        <f>(Raw_Data!E45-Raw_Data!E47)/F79</f>
+        <v>0.41426745788327335</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B90" t="s">
-        <v>111</v>
-      </c>
-      <c r="C90" s="17">
-        <v>0.1045</v>
-      </c>
-      <c r="D90" s="17">
-        <v>0.109</v>
-      </c>
-      <c r="E90" s="17">
-        <v>0.112</v>
+        <v>130</v>
+      </c>
+      <c r="C90" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="D90" s="5">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0.12</v>
       </c>
       <c r="F90" s="17">
-        <f>D66</f>
-        <v>0.10452249727541647</v>
+        <f>Raw_Data!E48/Raw_Data!E41</f>
+        <v>0.14165206547155104</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B91" t="s">
-        <v>112</v>
-      </c>
-      <c r="C91" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="D91" s="38">
-        <v>0.25</v>
-      </c>
-      <c r="E91" s="38">
-        <v>0.35</v>
-      </c>
-      <c r="F91" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B92" t="s">
-        <v>113</v>
-      </c>
-      <c r="C92" s="38">
-        <v>0.05</v>
-      </c>
-      <c r="D92" s="38">
-        <v>0.13</v>
-      </c>
-      <c r="E92" s="38">
-        <v>0.18</v>
-      </c>
-      <c r="F92" s="38">
-        <v>0</v>
+        <v>104</v>
+      </c>
+      <c r="C91" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="D91" s="5">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E91" s="5">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F91" s="17">
+        <f>(F80+Raw_Data!E40-Raw_Data!E48-Raw_Data!E49-Raw_Data!E46)/F80</f>
+        <v>7.5327459193251178E-2</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B93" t="s">
-        <v>99</v>
-      </c>
-      <c r="C93" s="41">
-        <v>1.85</v>
-      </c>
-      <c r="D93" s="41">
-        <v>1.8</v>
-      </c>
-      <c r="E93" s="41">
-        <v>1.75</v>
-      </c>
-      <c r="F93" s="41">
-        <f>D71</f>
-        <v>1.8163678877630554</v>
+        <v>105</v>
+      </c>
+      <c r="C93" s="18">
+        <f>C78*C88</f>
+        <v>400929.96</v>
+      </c>
+      <c r="D93" s="18">
+        <f t="shared" ref="D93:F93" si="0">D78*D88</f>
+        <v>482517.84586499998</v>
+      </c>
+      <c r="E93" s="18">
+        <f t="shared" si="0"/>
+        <v>529443.85200000007</v>
+      </c>
+      <c r="F93" s="18">
+        <f t="shared" si="0"/>
+        <v>433001</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B94" t="s">
-        <v>114</v>
-      </c>
-      <c r="C94" s="5">
-        <v>0.23</v>
-      </c>
-      <c r="D94" s="5">
-        <v>0.24</v>
-      </c>
-      <c r="E94" s="5">
-        <v>0.245</v>
-      </c>
-      <c r="F94" s="5">
-        <f>D70</f>
-        <v>0.24347217459080281</v>
+        <v>106</v>
+      </c>
+      <c r="C94" s="18">
+        <f>C79*C89</f>
+        <v>346629.92759999994</v>
+      </c>
+      <c r="D94" s="18">
+        <f t="shared" ref="D94:F94" si="1">D79*D89</f>
+        <v>437094.03780000005</v>
+      </c>
+      <c r="E94" s="18">
+        <f t="shared" si="1"/>
+        <v>507873.07800000004</v>
+      </c>
+      <c r="F94" s="18">
+        <f t="shared" si="1"/>
+        <v>372791</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B95" t="s">
-        <v>119</v>
-      </c>
-      <c r="C95" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="D95" s="5">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E95" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="F95" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>107</v>
+      </c>
+      <c r="C95" s="18">
+        <f>-(Raw_Data!$E$11*(1+C73)/C74)*C90</f>
+        <v>-1058127.5675675676</v>
+      </c>
+      <c r="D95" s="18">
+        <f>-(Raw_Data!$E$11*(1+D73)/D74)*D90</f>
+        <v>-1031396.1999999997</v>
+      </c>
+      <c r="E95" s="18">
+        <f>-(Raw_Data!$E$11*(1+E73)/E74)*E90</f>
+        <v>-942813.25714285707</v>
+      </c>
+      <c r="F95" s="18">
+        <f>-(Raw_Data!$E$11*(1+F73)/F74)*F90</f>
+        <v>-908697.99999999988</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B96" t="s">
+        <v>108</v>
+      </c>
+      <c r="C96" s="18">
+        <f>-C80*C91</f>
+        <v>-136895.25405405406</v>
+      </c>
+      <c r="D96" s="18">
+        <f t="shared" ref="D96:F96" si="2">-D80*D91</f>
+        <v>-131667.59999999995</v>
+      </c>
+      <c r="E96" s="18">
+        <f t="shared" si="2"/>
+        <v>-125119.17599999999</v>
+      </c>
+      <c r="F96" s="18">
+        <f t="shared" si="2"/>
+        <v>-117651.99999999999</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B97" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="C97" s="18">
-        <f>Raw_Data!$E$9*(1+C86)*C87 + Raw_Data!$E$27*(1+C88)</f>
-        <v>668216.60000000009</v>
+        <f>C82+C95+C96</f>
+        <v>-4629.3081081080309</v>
       </c>
       <c r="D97" s="18">
-        <f>Raw_Data!$E$9*(1+D86)*D87 + Raw_Data!$E$27*(1+D88)</f>
-        <v>734425.94499999995</v>
+        <f t="shared" ref="D97:F97" si="3">D82+D95+D96</f>
+        <v>409632.53333333333</v>
       </c>
       <c r="E97" s="18">
-        <f>Raw_Data!$E$9*(1+E86)*E87 + Raw_Data!$E$27*(1+E88)</f>
-        <v>778593.9</v>
-      </c>
-      <c r="F97" s="18">
-        <f>Raw_Data!$E$9*(1+F86)*F87 + Raw_Data!$E$27*(1+F88)</f>
-        <v>658726</v>
+        <f t="shared" si="3"/>
+        <v>699842.424</v>
+      </c>
+      <c r="F97" s="46">
+        <f>F82+F95+F96+Raw_Data!E40</f>
+        <v>354933.00000000012</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B98" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C98" s="18">
-        <f>Raw_Data!$E$30*(1+C89)*C90 + $D$67*(1+C91)</f>
-        <v>962860.90999999992</v>
+        <f>C93+C94+C97</f>
+        <v>742930.57949189201</v>
       </c>
       <c r="D98" s="18">
-        <f>Raw_Data!$E$30*(1+D89)*D90 + $D$67*(1+D91)</f>
-        <v>1055782.7000000002</v>
+        <f t="shared" ref="D98:F98" si="4">D93+D94+D97</f>
+        <v>1329244.4169983333</v>
       </c>
       <c r="E98" s="18">
-        <f>Raw_Data!$E$30*(1+E89)*E90 + $D$67*(1+E91)</f>
-        <v>1128606.8400000001</v>
-      </c>
-      <c r="F98" s="18">
-        <f>Raw_Data!$E$30*(1+F89)*F90 + $D$67*(1+F91)</f>
-        <v>899880</v>
-      </c>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B99" t="s">
-        <v>125</v>
-      </c>
-      <c r="C99" s="18">
-        <f>Raw_Data!$E$11*(1+C92)/C93*C94</f>
-        <v>1521058.3783783785</v>
-      </c>
-      <c r="D99" s="18">
-        <f>Raw_Data!$E$11*(1+D92)/D93*D94</f>
-        <v>1755567.9999999995</v>
-      </c>
-      <c r="E99" s="18">
-        <f>Raw_Data!$E$11*(1+E92)/E93*E94</f>
-        <v>1924910.4</v>
-      </c>
-      <c r="F99" s="18">
-        <f>Raw_Data!$E$11*(1+F92)/F93*F94</f>
-        <v>1561874</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B100" t="s">
-        <v>126</v>
-      </c>
-      <c r="C100" s="27">
-        <f>-(Raw_Data!$E$11*(1+C92)/C93)*C95</f>
-        <v>-330664.86486486485</v>
-      </c>
-      <c r="D100" s="27">
-        <f>-(Raw_Data!$E$11*(1+D92)/D93)*D95</f>
-        <v>-182871.66666666663</v>
-      </c>
-      <c r="E100" s="27">
-        <f>-(Raw_Data!$E$11*(1+E92)/E93)*E95</f>
-        <v>-157135.54285714286</v>
-      </c>
-      <c r="F100" s="27">
-        <f>-(Raw_Data!$E$11*(1+F92)/F93)*F95</f>
-        <v>-141130</v>
+        <f t="shared" si="4"/>
+        <v>1737159.3540000003</v>
+      </c>
+      <c r="F98" s="45">
+        <f t="shared" si="4"/>
+        <v>1160725</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B99" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C99" s="38">
+        <f>C98/C83</f>
+        <v>0.23569116491170497</v>
+      </c>
+      <c r="D99" s="38">
+        <f t="shared" ref="D99:F99" si="5">D98/D83</f>
+        <v>0.37488103456057748</v>
+      </c>
+      <c r="E99" s="38">
+        <f t="shared" si="5"/>
+        <v>0.45331653768267283</v>
+      </c>
+      <c r="F99" s="38">
+        <f t="shared" si="5"/>
+        <v>0.37197001743321539</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.5">
       <c r="B101" t="s">
-        <v>127</v>
-      </c>
-      <c r="C101" s="18">
-        <f>C99+C100</f>
-        <v>1190393.5135135136</v>
-      </c>
-      <c r="D101" s="18">
-        <f>D99+D100</f>
-        <v>1572696.333333333</v>
-      </c>
-      <c r="E101" s="18">
-        <f>E99+E100</f>
-        <v>1767774.857142857</v>
-      </c>
-      <c r="F101" s="18">
-        <f>F99+F100</f>
-        <v>1420744</v>
+        <v>122</v>
+      </c>
+      <c r="F101" s="5">
+        <f>Raw_Data!$E$7/Raw_Data!$E$3</f>
+        <v>0.26388716568209086</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B102" t="s">
-        <v>128</v>
-      </c>
-      <c r="C102" s="18">
-        <f>C97+C98+C99</f>
-        <v>3152135.8883783785</v>
-      </c>
-      <c r="D102" s="18">
-        <f>D97+D98+D99</f>
-        <v>3545776.6449999996</v>
-      </c>
-      <c r="E102" s="18">
-        <f>E97+E98+E99</f>
-        <v>3832111.14</v>
-      </c>
-      <c r="F102" s="18">
-        <f>F97+F98+F99</f>
-        <v>3120480</v>
+      <c r="B102" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="F102" s="5">
+        <f>(Raw_Data!$E$7-Raw_Data!$E$50)/(Raw_Data!$E$3-Raw_Data!$E$51)</f>
+        <v>0.382285339404422</v>
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B103" t="s">
-        <v>129</v>
-      </c>
-      <c r="C103" s="18">
-        <f>C97+C98+C101</f>
-        <v>2821471.0235135136</v>
-      </c>
-      <c r="D103" s="18">
-        <f>D97+D98+D101</f>
-        <v>3362904.978333333</v>
-      </c>
-      <c r="E103" s="18">
-        <f>E97+E98+E101</f>
-        <v>3674975.5971428575</v>
-      </c>
-      <c r="F103" s="18">
-        <f>F97+F98+F101</f>
-        <v>2979350</v>
-      </c>
-    </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B104" t="s">
-        <v>130</v>
-      </c>
-      <c r="C104" s="5">
-        <f>C102/$F$102-1</f>
-        <v>1.0144557368859441E-2</v>
-      </c>
-      <c r="D104" s="5">
-        <f>D102/$F$102-1</f>
-        <v>0.13629205923447651</v>
-      </c>
-      <c r="E104" s="5">
-        <f>E102/$F$102-1</f>
-        <v>0.22805181895093063</v>
-      </c>
-      <c r="F104" s="5">
-        <f>F102/$F$102-1</f>
+      <c r="B103" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F103" s="34">
+        <f>F98-(Raw_Data!E7-Raw_Data!E47)</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B106" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D106" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E106" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="F106" s="25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B107" t="s">
-        <v>132</v>
-      </c>
-      <c r="C107" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D107" s="5">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="E107" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="F107" s="17">
-        <f>433000/$F$97</f>
-        <v>0.65732945109195628</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B108" t="s">
-        <v>133</v>
-      </c>
-      <c r="C108" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="D108" s="5">
-        <v>0.311</v>
-      </c>
-      <c r="E108" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="F108" s="17">
-        <f>280000/$F$98</f>
-        <v>0.31115259812419432</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B109" t="s">
-        <v>134</v>
-      </c>
-      <c r="C109" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="D109" s="5">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="E109" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="F109" s="17">
-        <f>909000/Raw_Data!$E$41</f>
-        <v>0.14169914263445052</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B110" t="s">
-        <v>135</v>
-      </c>
-      <c r="C110" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="D110" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="E110" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="F110" s="17">
-        <v>0.1004</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B112" t="s">
-        <v>136</v>
-      </c>
-      <c r="C112" s="18">
-        <f>C97*C107</f>
-        <v>400929.96</v>
-      </c>
-      <c r="D112" s="18">
-        <f t="shared" ref="D112:F112" si="0">D97*D107</f>
-        <v>482517.84586499998</v>
-      </c>
-      <c r="E112" s="18">
-        <f t="shared" si="0"/>
-        <v>529443.85200000007</v>
-      </c>
-      <c r="F112" s="18">
-        <f t="shared" si="0"/>
-        <v>433000</v>
-      </c>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B113" t="s">
-        <v>137</v>
-      </c>
-      <c r="C113" s="18">
-        <f>C98*C108</f>
-        <v>240715.22749999998</v>
-      </c>
-      <c r="D113" s="18">
-        <f t="shared" ref="D113:F113" si="1">D98*D108</f>
-        <v>328348.41970000003</v>
-      </c>
-      <c r="E113" s="18">
-        <f t="shared" si="1"/>
-        <v>395012.39400000003</v>
-      </c>
-      <c r="F113" s="18">
-        <f t="shared" si="1"/>
-        <v>280000</v>
-      </c>
-    </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B114" t="s">
-        <v>138</v>
-      </c>
-      <c r="C114" s="18">
-        <f>-(Raw_Data!$E$11*(1+C92)/C93)*C109</f>
-        <v>-1058127.5675675676</v>
-      </c>
-      <c r="D114" s="18">
-        <f>-(Raw_Data!$E$11*(1+D92)/D93)*D109</f>
-        <v>-1031396.1999999997</v>
-      </c>
-      <c r="E114" s="18">
-        <f>-(Raw_Data!$E$11*(1+E92)/E93)*E109</f>
-        <v>-942813.25714285707</v>
-      </c>
-      <c r="F114" s="18">
-        <f>-(Raw_Data!$E$11*(1+F92)/F93)*F109</f>
-        <v>-909000.00000000012</v>
-      </c>
-    </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B115" t="s">
-        <v>139</v>
-      </c>
-      <c r="C115" s="18">
-        <f>-C99*C110</f>
-        <v>-197737.5891891892</v>
-      </c>
-      <c r="D115" s="18">
-        <f t="shared" ref="D115:F115" si="2">-D99*D110</f>
-        <v>-175556.79999999996</v>
-      </c>
-      <c r="E115" s="18">
-        <f t="shared" si="2"/>
-        <v>-173241.93599999999</v>
-      </c>
-      <c r="F115" s="18">
-        <f t="shared" si="2"/>
-        <v>-156812.1496</v>
-      </c>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B116" t="s">
-        <v>140</v>
-      </c>
-      <c r="C116" s="18">
-        <f>C101+C114+C115</f>
-        <v>-65471.643243243161</v>
-      </c>
-      <c r="D116" s="18">
-        <f t="shared" ref="D116:F116" si="3">D101+D114+D115</f>
-        <v>365743.33333333337</v>
-      </c>
-      <c r="E116" s="18">
-        <f t="shared" si="3"/>
-        <v>651719.66399999999</v>
-      </c>
-      <c r="F116" s="18">
-        <f t="shared" si="3"/>
-        <v>354931.85039999988</v>
-      </c>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B117" t="s">
-        <v>141</v>
-      </c>
-      <c r="C117" s="18">
-        <f>C112+C113+C116</f>
-        <v>576173.54425675678</v>
-      </c>
-      <c r="D117" s="18">
-        <f t="shared" ref="D117:F117" si="4">D112+D113+D116</f>
-        <v>1176609.5988983335</v>
-      </c>
-      <c r="E117" s="18">
-        <f t="shared" si="4"/>
-        <v>1576175.9100000001</v>
-      </c>
-      <c r="F117" s="52">
-        <f t="shared" si="4"/>
-        <v>1067931.8503999999</v>
-      </c>
-    </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.5">
-      <c r="B118" t="s">
-        <v>142</v>
-      </c>
-      <c r="C118" s="17">
-        <f>C117/C102</f>
-        <v>0.18278829487683357</v>
-      </c>
-      <c r="D118" s="17">
-        <f t="shared" ref="D118:F118" si="5">D117/D102</f>
-        <v>0.33183409918318013</v>
-      </c>
-      <c r="E118" s="17">
-        <f t="shared" si="5"/>
-        <v>0.41130746275798258</v>
-      </c>
-      <c r="F118" s="17">
-        <f t="shared" si="5"/>
-        <v>0.34223319822591391</v>
       </c>
     </row>
   </sheetData>

--- a/Kaspi_Financial_Analysis.xlsx
+++ b/Kaspi_Financial_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consulting\Kaspi Bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707EFB8C-8E75-4159-99A0-460817265065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0150BBF-707D-4E2A-966D-866B9DB1E607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{74D3D57B-FAE8-45A6-AD25-DA4D42E998AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{74D3D57B-FAE8-45A6-AD25-DA4D42E998AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -719,8 +719,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE31937"/>
       <color rgb="FFBA1616"/>
-      <color rgb="FFE31937"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1329,7 +1329,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="E31937"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1442,7 +1442,10 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1532,13 +1535,13 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>742930.57949189201</c:v>
+                  <c:v>742930.5794918919</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1329244.4169983333</c:v>
+                  <c:v>1321929.5503316666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1737159.3540000003</c:v>
+                  <c:v>1725374.1882857145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1558,8 +1561,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:gapWidth val="120"/>
+        <c:overlap val="-16"/>
         <c:axId val="215199167"/>
         <c:axId val="215201663"/>
       </c:barChart>
@@ -1664,6 +1667,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Inter Tight" pitchFamily="2" charset="0"/>
+              <a:ea typeface="Inter Tight" pitchFamily="2" charset="0"/>
+              <a:cs typeface="Inter Tight" pitchFamily="2" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-KZ"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -4978,8 +5012,8 @@
       <c r="D48" s="36">
         <v>616116</v>
       </c>
-      <c r="E48" s="36">
-        <v>908698</v>
+      <c r="E48" s="18">
+        <v>763964</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.5">
@@ -4992,8 +5026,8 @@
       <c r="D49" s="36">
         <v>113957</v>
       </c>
-      <c r="E49" s="36">
-        <v>161651</v>
+      <c r="E49" s="18">
+        <v>150798</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.5">
@@ -5470,7 +5504,7 @@
       </c>
       <c r="E33" s="26"/>
     </row>
-    <row r="34" spans="2:11" ht="42" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.5">
       <c r="B34" s="27" t="s">
         <v>47</v>
       </c>
@@ -6006,17 +6040,17 @@
         <v>129</v>
       </c>
       <c r="C76" s="5">
-        <v>0.05</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="D76" s="5">
-        <v>2.5000000000000001E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="E76" s="5">
-        <v>0.02</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F76" s="17">
         <f>Raw_Data!E49/Raw_Data!E41</f>
-        <v>2.5198908807482462E-2</v>
+        <v>2.3507092751363992E-2</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.5">
@@ -6088,19 +6122,19 @@
       </c>
       <c r="C81" s="23">
         <f>-(Raw_Data!$E$11*(1+C73)/C74)*C76</f>
-        <v>-330664.86486486485</v>
+        <v>-324051.56756756757</v>
       </c>
       <c r="D81" s="23">
         <f>-(Raw_Data!$E$11*(1+D73)/D74)*D76</f>
-        <v>-182871.66666666663</v>
+        <v>-175556.79999999996</v>
       </c>
       <c r="E81" s="23">
         <f>-(Raw_Data!$E$11*(1+E73)/E74)*E76</f>
-        <v>-157135.54285714286</v>
+        <v>-149278.76571428572</v>
       </c>
       <c r="F81" s="23">
         <f>-(Raw_Data!$E$11*(1+F73)/F74)*F76</f>
-        <v>-161651</v>
+        <v>-150798</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.5">
@@ -6109,19 +6143,19 @@
       </c>
       <c r="C82" s="18">
         <f>C80+C81</f>
-        <v>1190393.5135135136</v>
+        <v>1197006.8108108109</v>
       </c>
       <c r="D82" s="18">
         <f>D80+D81</f>
-        <v>1572696.333333333</v>
+        <v>1580011.1999999995</v>
       </c>
       <c r="E82" s="18">
         <f>E80+E81</f>
-        <v>1767774.857142857</v>
+        <v>1775631.6342857142</v>
       </c>
       <c r="F82" s="18">
         <f>F80+F81</f>
-        <v>1400223</v>
+        <v>1411076</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.5">
@@ -6151,19 +6185,19 @@
       </c>
       <c r="C84" s="18">
         <f>C78+C79+C82</f>
-        <v>2821471.0235135136</v>
+        <v>2828084.3208108107</v>
       </c>
       <c r="D84" s="18">
         <f>D78+D79+D82</f>
-        <v>3362904.978333333</v>
+        <v>3370219.8449999997</v>
       </c>
       <c r="E84" s="18">
         <f>E78+E79+E82</f>
-        <v>3674975.5971428575</v>
+        <v>3682832.3742857147</v>
       </c>
       <c r="F84" s="18">
         <f>F78+F79+F82</f>
-        <v>2958829</v>
+        <v>2969682</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.5">
@@ -6245,17 +6279,17 @@
         <v>130</v>
       </c>
       <c r="C90" s="5">
-        <v>0.16</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="D90" s="5">
-        <v>0.14099999999999999</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="E90" s="5">
-        <v>0.12</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="F90" s="17">
         <f>Raw_Data!E48/Raw_Data!E41</f>
-        <v>0.14165206547155104</v>
+        <v>0.11909025720966485</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.5">
@@ -6263,17 +6297,17 @@
         <v>104</v>
       </c>
       <c r="C91" s="5">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="D91" s="5">
-        <v>7.4999999999999997E-2</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="E91" s="5">
-        <v>6.5000000000000002E-2</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="F91" s="17">
         <f>(F80+Raw_Data!E40-Raw_Data!E48-Raw_Data!E49-Raw_Data!E46)/F80</f>
-        <v>7.5327459193251178E-2</v>
+        <v>0.17494304918322476</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.5">
@@ -6324,19 +6358,19 @@
       </c>
       <c r="C95" s="18">
         <f>-(Raw_Data!$E$11*(1+C73)/C74)*C90</f>
-        <v>-1058127.5675675676</v>
+        <v>-912635.0270270271</v>
       </c>
       <c r="D95" s="18">
         <f>-(Raw_Data!$E$11*(1+D73)/D74)*D90</f>
-        <v>-1031396.1999999997</v>
+        <v>-870469.13333333307</v>
       </c>
       <c r="E95" s="18">
         <f>-(Raw_Data!$E$11*(1+E73)/E74)*E90</f>
-        <v>-942813.25714285707</v>
+        <v>-769964.16</v>
       </c>
       <c r="F95" s="18">
         <f>-(Raw_Data!$E$11*(1+F73)/F74)*F90</f>
-        <v>-908697.99999999988</v>
+        <v>-763964</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.5">
@@ -6345,19 +6379,19 @@
       </c>
       <c r="C96" s="18">
         <f>-C80*C91</f>
-        <v>-136895.25405405406</v>
+        <v>-289001.09189189191</v>
       </c>
       <c r="D96" s="18">
         <f t="shared" ref="D96:F96" si="2">-D80*D91</f>
-        <v>-131667.59999999995</v>
+        <v>-307224.39999999991</v>
       </c>
       <c r="E96" s="18">
         <f t="shared" si="2"/>
-        <v>-125119.17599999999</v>
+        <v>-317610.21600000001</v>
       </c>
       <c r="F96" s="18">
         <f t="shared" si="2"/>
-        <v>-117651.99999999999</v>
+        <v>-273239</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.5">
@@ -6366,19 +6400,19 @@
       </c>
       <c r="C97" s="18">
         <f>C82+C95+C96</f>
-        <v>-4629.3081081080309</v>
+        <v>-4629.3081081081182</v>
       </c>
       <c r="D97" s="18">
-        <f t="shared" ref="D97:F97" si="3">D82+D95+D96</f>
-        <v>409632.53333333333</v>
+        <f t="shared" ref="D97:E97" si="3">D82+D95+D96</f>
+        <v>402317.66666666651</v>
       </c>
       <c r="E97" s="18">
         <f t="shared" si="3"/>
-        <v>699842.424</v>
+        <v>688057.2582857142</v>
       </c>
       <c r="F97" s="46">
         <f>F82+F95+F96+Raw_Data!E40</f>
-        <v>354933.00000000012</v>
+        <v>354933</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.5">
@@ -6387,15 +6421,15 @@
       </c>
       <c r="C98" s="18">
         <f>C93+C94+C97</f>
-        <v>742930.57949189201</v>
+        <v>742930.5794918919</v>
       </c>
       <c r="D98" s="18">
         <f t="shared" ref="D98:F98" si="4">D93+D94+D97</f>
-        <v>1329244.4169983333</v>
+        <v>1321929.5503316666</v>
       </c>
       <c r="E98" s="18">
         <f t="shared" si="4"/>
-        <v>1737159.3540000003</v>
+        <v>1725374.1882857145</v>
       </c>
       <c r="F98" s="45">
         <f t="shared" si="4"/>
@@ -6408,15 +6442,15 @@
       </c>
       <c r="C99" s="38">
         <f>C98/C83</f>
-        <v>0.23569116491170497</v>
+        <v>0.23569116491170491</v>
       </c>
       <c r="D99" s="38">
         <f t="shared" ref="D99:F99" si="5">D98/D83</f>
-        <v>0.37488103456057748</v>
+        <v>0.37281805445804295</v>
       </c>
       <c r="E99" s="38">
         <f t="shared" si="5"/>
-        <v>0.45331653768267283</v>
+        <v>0.45024116609668957</v>
       </c>
       <c r="F99" s="38">
         <f t="shared" si="5"/>
